--- a/TodAI_Lessons_1-98 Optimized.xlsx
+++ b/TodAI_Lessons_1-98 Optimized.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capgemini-my.sharepoint.com/personal/bertrand-philippe-guillaume_caeymae_capgemini_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8ACCD3FB-A931-4D52-9D0F-11E3F542D50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A22F413A-2E80-4130-AED4-94EAA1ED8361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="753">
   <si>
     <t>Block Number</t>
   </si>
@@ -372,17 +372,6 @@
 So in simple terms, AI organizes the mess, and you confirm the meaning.</t>
   </si>
   <si>
-    <t>Key Takeaways
-• Categories reveal different types of information.
-• Unconfirmed details must remain unconfirmed.
-• Clean structure makes the next action visible.
-Golden Rule
-Ask AI to organize what exists, not complete what is missing.
-Next Step
-Create three reusable headings for your next notes page before the conversation begins.
-10-20</t>
-  </si>
-  <si>
     <t>What AI Actually Is (and Isn't)</t>
   </si>
   <si>
@@ -681,12 +670,6 @@
 The aim is to choose five different situations, apply the right beginner skill, and remain responsible for each outcome. Small wins reveal where AI fits naturally into your day.</t>
   </si>
   <si>
-    <t>Step 1: Identify five safe tasks with different desired results.
-Step 2: Choose an appropriate AI approach for each task.
-Step 3: review every output and record what changed because of your input.
-So in simple terms, use AI five times with purpose, variety, and human judgment.</t>
-  </si>
-  <si>
     <t>Situation
 Mei wants to test whether AI can support a normal weekday without taking over her decisions.
 Without AI
@@ -706,45 +689,6 @@
 3. Record which task you would repeat.
 Success Criteria
 You finish with five distinct outputs and one evidence-based reusable use case.</t>
-  </si>
-  <si>
-    <t>Key Takeaways
-• A win requires a useful result.
-• Different tasks may require different approaches.
-• Review turns AI output into human-approved work.
-Golden Rule
-Count completed outcomes, not AI conversations.
-Next Step
-Save your strongest use case as the first entry in a personal AI playbook.
-20-30
-Block 2: How AI Actually Thinks
-Block Purpose
-This block gives learners a practical mental model of how language-based AI produces answers and why those answers sometimes fail. The goal is not technical mastery, but better decisions, clearer interactions, and fewer avoidable mistakes.
-Learner Transformation
-By the end of this block, learners will move from using AI based on appearances to predicting its behaviour and responding to its limitations.
-Progression Logic
-The block begins with language models and next-word prediction. It then shows how text becomes tokens, why calculation is a special challenge, and how limited context affects long conversations. The batch finishes by separating stored model knowledge from live search and teaching learners to recognize and reduce hallucinations.
-Lessons in This Batch
-• 
-1. What a Large Language Model Is
-• 
-1. Next-Word Prediction, Seen Live
-• 
-1. Tokens: Why AI Miscounts Letters
-• 
-1. Why It Fails at Math — and How to Fix It
-• 
-1. The Context Window: How Much It Holds
-• 
-1. Why Long Chats Go Off the Rails (and the Restart Trick)
-• 
-1. Training Data and Knowledge Cutoffs
-• 
-1. Connected vs. Offline: AI That Can Search
-• 
-1. Hallucinations: Catch One on Purpose
-• 
-1. Three Habits That Cut Hallucinations</t>
   </si>
   <si>
     <t>How AI Actually Thinks</t>
@@ -1075,10 +1019,6 @@
     <t>After completing this lesson, learners will be able to choose between a quick response and deeper task processing.</t>
   </si>
   <si>
-    <t>Some AI models prioritize speed for straightforward requests. Others are designed to spend more effort on tasks involving several constraints, connected decisions, or careful analysis.
-A longer response time does not automatically guarantee a better answer. Simple tasks rarely need heavy processing. The useful question is whether the task requires quick language support or deliberate problem- solving.</t>
-  </si>
-  <si>
     <t>Step 1: Estimate the task’s complexity and the cost of a weak answer.
 Step 2: Choose a faster option for simple transformations or a reasoning option for connected decisions.
 Step 3: Review whether the extra processing improved the result.
@@ -1333,44 +1273,6 @@
 Step 2: Run it unchanged in up to four available assistants.
 Step 3: Score each output using the same short rubric and record your observations.
 So in simple terms, control the request, compare the evidence, and choose for the task.</t>
-  </si>
-  <si>
-    <t>Key Takeaways
-• Controlled tests reveal meaningful differences.
-• Polished language cannot replace source accuracy.
-• Tool choice should remain task-specific.
-Golden Rule
-Compare behaviours, not brands.
-Next Step
-Keep your rubric and repeat the test when your task or available models change.
-Block 3: The Art of Asking
-Block Purpose
-This block teaches learners how to guide AI deliberately instead of hoping it interprets a vague request correctly. Learners will build prompts by defining the task, adding useful context, identifying the audience, and controlling tone, length, and format.
-Learner Transformation
-By the end of this block, learners will move from writing basic requests to shaping AI outputs with clear, reusable instructions.
-Progression Logic
-The block begins by showing what makes a prompt effective and how specificity changes the result. Learners then build prompts from four practical elements before exploring each element separately. This batch finishes with control over audience, role, tone, length, and format. Later lessons will add constraints, examples, document handling, and refinement.
-Lessons in This Batch
-• 
-1. What Makes a Prompt Work
-• 
-1. Before and After: Vague vs. Specific
-• 
-1. The Four Building Blocks of Any Prompt
-• 
-1. State the Task in One Clear Sentence
-• 
-1. Context: The Detail That Changes Everything
-• 
-1. Who Is This For? Writing for an Audience
-• 
-1. Giving the AI a Role — and When It's Useless
-• 
-1. Same Message, Five Different Tones
-• 
-1. Controlling Length
-• 
-1. Ask for the Format You Actually Need</t>
   </si>
   <si>
     <t>The Art of Asking</t>
@@ -2036,18 +1938,6 @@
 So in simple terms, describe the issue clearly and move the conversation toward resolution.</t>
   </si>
   <si>
-    <t>Situation
-Daniel lent a camera to a friend, who has twice missed the agreed return date. Daniel needs it for a course on Saturday.
-Without AI
-He keeps postponing the message because his first draft sounds angry: “You never respect deadlines.”
-With AI
-Daniel asks:
-“Draft a respectful but firm message. The camera was due back twice, and I need it by Friday evening for a Saturday course. Ask for a specific collection time. Do not accuse or threaten.”
-AI produces a calm draft. Daniel adds two collection windows he can genuinely offer.
-Result
-Daniel sends a factual message with a clear Friday deadline and receives confirmation of a 18:30 collection.</t>
-  </si>
-  <si>
     <t>Your Mission
 Structure a difficult fictional message.
 Instructions
@@ -2248,46 +2138,6 @@
 3. Rewrite and test it using two success criteria.
 Success Criteria
 The revised output is measurably more relevant, usable, or correctly structured.</t>
-  </si>
-  <si>
-    <t>Key Takeaways
-• Prompt improvement begins with diagnosis.
-• Useful detail solves a specific weakness.
-• Clear criteria reveal whether the revision worked.
-Golden Rule
-Do not decorate a broken prompt. Repair the missing instruction.
-Next Step
-Save the improved prompt with a short note explaining what changed and why.
-Block 4: From Prompts to Systems
-Block Purpose
-This block teaches learners to turn individual prompts into repeatable systems for more complex tasks. Learners will structure requests, divide work into stages, connect outputs, and introduce practical quality checks.
-Learner Transformation
-By the end of this block, learners will move from improving single prompts to building structured, repeatable AI processes.
-Progression Logic
-The block begins by showing why repeatable structure improves consistency. Learners compare two lightweight prompt frameworks, practise choosing between them, and then move into planning, task decomposition, and prompt chains. The batch ends by adding self-critique, rubrics, and plan-first workflows.
-Lessons in This Batch
-• 
-1. From Prompt to System: Why Structure Wins
-• 
-1. RTF: Role, Task, Format
-• 
-1. RACE: Role, Action, Context, Expectation
-• 
-1. Picking a Framework in Ten Seconds
-• 
-1. Step-by-Step Thinking
-• 
-1. Splitting a Big Job Into Steps
-• 
-1. Chain Prompting: One Output Feeds the Next
-• 
-1. Chain in Action: Idea → Outline → Draft → Polish
-• 
-1. Ask the AI to Critique Its Own Work
-• 
-1. The Rubric Trick: Score It, Then Fix It
-• 
-1. Plan First, Write Second</t>
   </si>
   <si>
     <t>From Prompts to Systems</t>
@@ -3578,12 +3428,6 @@
 The challenge is not to create the longest workflow. It is to make every stage necessary and reviewable. A final quality check confirms that weak information did not travel silently through the chain.</t>
   </si>
   <si>
-    <t>Step 1: Define the final deliverable and the three intermediate outputs it requires.
-Step 2: arrange the four stages in dependency order.
-Step 3: Review each output before passing it to the next stage.
-So in simple terms, build four necessary links and inspect every handover.</t>
-  </si>
-  <si>
     <t>Situation
 Elisa wants to create an orientation sheet for volunteers at a public reading festival.
 Without AI
@@ -3694,19 +3538,6 @@
 She sends a concise message that communicates the delay without sounding careless or overly formal.
 Key Insight
 You can now improve an email while preserving its meaning and personal voice.</t>
-  </si>
-  <si>
-    <t>Situation
-Iris wants help planning a short presentation from notes stored in her workplace tools.
-What to Notice
-Iris first defines the task: create a five-slide outline from approved notes. She checks which assistant her organization allows for that content and whether it can work in the relevant environment.
-She then tests it with non-sensitive material before using workplace information.
-Why It Matters
-Iris selects an accessible, approved option and receives a five-slide outline without moving information into an unsuitable tool.
-Quick Check
-What should the learner trust, verify, choose, or keep under human control in this situation?
-Key Insight
-Choose among major ai assistants based on task and access.</t>
   </si>
   <si>
     <t>Situation
@@ -3786,36 +3617,6 @@
   </si>
   <si>
     <t>Situation
-Diego considers buying an AI subscription after seeing several premium feature descriptions.
-What to Notice
-Diego writes down his actual needs: generate study questions, simplify difficult paragraphs, and create weekly revision plans. He tests each task with his available option and records whether a feature, limit, or quality issue blocks him.
-All three tasks work well enough for his current routine.
-Why It Matters
-Diego postpones the subscription and sets a clear trigger for reconsidering it: a repeated study task that his current access cannot complete reliably.
-Quick Check
-What should the learner trust, verify, choose, or keep under human control in this situation?
-Key Insight
-Decide whether a paid ai option supports a genuine need.</t>
-  </si>
-  <si>
-    <t>Situation
-Owen regularly needs to turn webinar descriptions into short entries for his learning journal.
-Try It Yourself
-Build a one-placeholder prompt.
-1. Choose a harmless recurring task.
-2. Write the fixed instruction.
-3. Replace the changing content with [INPUT].
-Observe
-Someone else could identify exactly what to replace and what result to expect.
-What Happened?
-is too formal, so he adds: “Use clear first-person language.”
-Result
-Owen has a reusable prompt with one obvious placeholder and a consistent three-part output for future journal entries.
-Key Insight
-You can now create and save a reusable prompt for a recurring task.</t>
-  </si>
-  <si>
-    <t>Situation
 Ben starts the sentence: “She opened the umbrella because”
 Try It Yourself
 Predict what comes next.
@@ -3876,23 +3677,6 @@
   </si>
   <si>
     <t>Situation
-Nadine wants to find public library opening hours for an upcoming public holiday.
-Try It Yourself
-Identify the evidence behind an answer.
-1. Ask a harmless question about current information.
-2. Look for a source and publication date.
-3. Decide whether the answer shows live retrieval.
-Observe
-You can state what source was used or say that no source was shown.
-What Happened?
-from the library’s official website. Nadine opens the source and notices that different branches have different hours.
-Result
-She records the correct schedule for her chosen branch instead of relying on a general timetable.
-Key Insight
-You can now determine whether an AI answer uses live sources or stored model knowledge.</t>
-  </si>
-  <si>
-    <t>Situation
 Andre invents a fictional business book titled The Quiet Deadline by Maria Velden and asks for its main argument.
 Try It Yourself
 Run a safe hallucination test.
@@ -3905,61 +3689,6 @@
 Andre catches a hallucination deliberately and identifies the unsupported title, author, and argument.
 Key Insight
 You can now recognize an invented AI claim that appears plausible.</t>
-  </si>
-  <si>
-    <t>Situation
-Leila needs a short biography for a speaker at a neighbourhood science event.
-Try It Yourself
-Apply the three anti-hallucination habits.
-1. Provide a short factual paragraph.
-2. Request two facts using only that text.
-3. Match both answers to supporting sentences.
-Observe
-Every generated fact has visible support in the supplied material.
-What Happened?
-with the profile and removes one ambiguous description.
-Result
-Leila produces an accurate biography containing only confirmed experience, research interests, and the speaker’s current role.
-Key Insight
-You can now apply three habits that reduce unsupported AI claims.</t>
-  </si>
-  <si>
-    <t>Situation
-Aisha needs a slogan for a weekend repair café where volunteers help people fix household items.
-Try It Yourself
-Observe useful variation.
-1. Ask AI for three names for a fictional café.
-2. Repeat the exact request.
-3. Compare which names changed and which qualities remained.
-Observe
-You identify at least one difference and choose an option using a clear criterion.
-What Happened?
-is different, but she has no way to decide which one works best.
-With AI
-Aisha defines three criteria: friendly, under six words, and focused on repairing rather than replacing. She requests five options and evaluates each against those criteria.
-The alternatives still vary, but the rules remain stable.
-Result
-Aisha selects “Fix More, Waste Less” because it meets all three criteria. Variation gives her choices, while her criteria provide consistency.
-Key Insight
-You can now manage variation when AI produces different answers to the same request.</t>
-  </si>
-  <si>
-    <t>Situation
-Min wants a simple explanation of compound interest for a youth savings club.
-Try It Yourself
-Run a fair assistant comparison.
-1. Choose one harmless request.
-2. Use it unchanged in two available assistants.
-3. Compare the outputs using two criteria.
-Observe
-You choose one result and justify the choice with evidence from the outputs.
-What Happened?
-s for clarity, age suitability, example quality, and unnecessary jargon.
-One response is accurate but too technical. Another is simple but misses how interest builds over time. A third explains the idea clearly with a short numerical example.
-Result
-Min selects the third explanation for the club and records why it fits this audience. She does not assume the same assistant will be best for every future task.
-Key Insight
-You can now compare AI assistants using the same task and evaluation criteria.</t>
   </si>
   <si>
     <t>Situation
@@ -4096,23 +3825,6 @@
   </si>
   <si>
     <t>Situation
-Hugo needs to explain a new recycling station to children visiting a nature centre.
-Try It Yourself
-Change content for a new audience.
-1. Choose one simple topic.
-2. Name two audiences with different knowledge levels.
-3. Write one sentence explaining what each audience needs.
-Observe
-The two audience descriptions would lead to visibly different content.
-What Happened?
-ing explanation uses familiar objects and short instructions. Hugo checks that each bin description matches the centre’s actual system.
-Result
-He creates a four-part sign that children can use to sort paper, containers, food waste, and general rubbish.
-Key Insight
-You can now adapt AI-generated content for a clearly defined audience.</t>
-  </si>
-  <si>
-    <t>Situation
 Zara has drafted instructions for borrowing equipment from a youth club.
 Try It Yourself
 Remove a decorative role.
@@ -4323,29 +4035,6 @@
   </si>
   <si>
     <t>Situation
-Tariq prepares a weekly update for his amateur basketball group.
-Try It Yourself
-Turn one repeated task into a system.
-1. Choose a harmless recurring task.
-2. Write its input, process, and review step.
-3. Identify which information changes each time.
-Observe
-Your system can be reused without redesigning the whole process.
-What Happened?
-s, others include upcoming games, and several forget venue information.
-With AI
-Tariq creates a three-part system:
-1. Provide this week’s approved notes.
-2. Generate sections for Results, Next Game, and Important Updates.
-3. Check every date and location against the notes.
-The weekly details change, but the process and output remain stable.
-Result
-Tariq produces a consistent update containing the same three useful sections every week, with dates and venues checked before publication.
-Key Insight
-You can now turn a recurring AI task into a simple, repeatable process.</t>
-  </si>
-  <si>
-    <t>Situation
 Beatriz is preparing labels for objects displayed at a local science fair.
 Try It Yourself
 Create an RTF prompt.
@@ -4416,12 +4105,1816 @@
   <si>
     <t xml:space="preserve">Advanced </t>
   </si>
+  <si>
+    <t>Question
+ Emma has never used AI before. Which of these is the best first task?
+Option A
+ Ask AI to create a complete 5-year career plan.
+Option B
+ Ask AI to choose the best city for her to live in.
+Option C
+ Ask AI to organize her shopping list into categories before going to the supermarket.
+Option D
+ Ask AI to predict what job she will have in ten years.
+Correct Answer
+ C
+Explanation
+ The best first AI task is small, real, and immediately useful. Organizing a shopping list produces a clear result that Emma can easily review. The other options are much broader and involve bigger decisions.</t>
+  </si>
+  <si>
+    <t>Question
+ While typing a message, Julia's phone suggests the next word she may want to write. What is the AI mainly doing?
+Option A
+ Reading Julia's thoughts.
+Option B
+ Predicting a likely next word based on patterns.
+Option C
+ Choosing what Julia should say.
+Option D
+ Checking whether the message is true.
+Correct Answer
+ B
+Explanation
+ Many AI systems work by recognizing patterns and making predictions. The keyboard is predicting what word may come next, not reading thoughts or deciding what Julia should write.</t>
+  </si>
+  <si>
+    <t>Question
+ Laura is working inside a spreadsheet and wants help understanding a table that is already open on her screen. Which option is usually the most efficient?
+Option A
+ Use an approved AI feature built into the spreadsheet application.
+Option B
+ Copy everything manually into a separate AI chat.
+Option C
+ Create a brand-new document and rewrite the data there.
+Option D
+ Take notes first and ask the AI later.
+Correct Answer
+ A
+Explanation
+ When the information already exists inside an application, a built-in AI assistant can use that context more efficiently than moving information elsewhere.</t>
+  </si>
+  <si>
+    <t>Question
+ A photo app becomes better at recognizing different dog breeds after being trained on thousands of labeled images. What best explains how it improved?
+Option A
+ Developers manually wrote a rule for every breed.
+Option B
+ The system learned patterns from many examples and applied them to new photos.
+Option C
+ The app searches the internet whenever a new picture is uploaded.
+Option D
+ The app understands what a dog is in the same way a human does.
+Correct Answer
+ B
+Explanation
+ Machine learning works by learning patterns from examples. The system then uses those patterns when it encounters new images.</t>
+  </si>
+  <si>
+    <t>Question
+ During one conversation, an AI remembers that Chris prefers short answers and continues responding that way. What is the safest conclusion?
+Option A
+ The AI has permanently retrained itself using Chris's information.
+Option B
+ The AI is likely using information from the current conversation context.
+Option C
+ The AI now remembers Chris forever.
+Option D
+ The AI has changed its underlying model specifically for Chris.
+Correct Answer
+ B
+Explanation
+ Adapting within a conversation does not automatically mean the model is being retrained. Often, the AI is simply using information already provided in the current interaction.</t>
+  </si>
+  <si>
+    <t>Question
+ An AI confidently provides a historical date that sounds completely believable. What is the best response?
+Option A
+ Trust the date because the explanation sounds detailed.
+Option B
+ Treat the confident tone as evidence that the date is correct.
+Option C
+ Ignore the answer completely because AI is never accurate.
+Option D
+ Verify the date using a reliable source before relying on it.
+Correct Answer
+ D
+Explanation
+ Fluent and confident writing is not proof of accuracy. Important facts should be checked independently.</t>
+  </si>
+  <si>
+    <t>Question
+ A bookstore owner uploads 50 customer reviews and asks AI to identify the main themes customers mention. What is the AI primarily doing?
+Option A
+ Checking whether every opinion is true.
+Option B
+ Recognizing language patterns across the reviews.
+Option C
+ Reading the customers' intentions directly.
+Option D
+ Retrieving the reviews from memory.
+Correct Answer
+ B
+Explanation
+ Large Language Models work by identifying patterns in language. In this case, the AI is finding recurring ideas and themes across many reviews rather than understanding the customers like a human would.</t>
+  </si>
+  <si>
+    <t>Question
+ An AI completes the sentence: "The picnic was moved indoors because..." What best explains how it generates the rest of the sentence?
+Option A
+ It finds the one correct ending stored in its database.
+Option B
+ It chooses a continuation randomly.
+Option C
+ It predicts likely continuations based on the context provided.
+Option D
+ It searches the internet for the answer.
+Correct Answer
+ C
+Explanation
+ Language models generate text by predicting what is likely to come next based on the words and context already available.</t>
+  </si>
+  <si>
+    <t>Question
+ During a long project conversation, AI suddenly forgets a key requirement mentioned at the beginning. What is the best response?
+Option A
+ Assume AI will eventually remember it automatically.
+Option B
+ Ignore the requirement and continue.
+Option C
+ Provide a short summary of the important constraints again.
+Option D
+ Start asking unrelated questions.
+Correct Answer
+ C
+Explanation
+ AI has limited working context. Reintroducing key requirements helps keep important information visible and available.</t>
+  </si>
+  <si>
+    <t>Question
+ You ask AI to summarize a book that does not actually exist. The AI confidently provides a plot, characters, and key lessons. What has most likely happened?
+Option A
+ The AI discovered a hidden version of the book.
+Option B
+ The AI filled the information gap with plausible-sounding invented content.
+Option C
+ The AI found the author's unpublished notes.
+Option D
+ The AI translated the title incorrectly.
+Correct Answer
+ B
+Explanation
+ This is a classic hallucination. When information is unavailable, AI may generate a convincing but unsupported answer.</t>
+  </si>
+  <si>
+    <t>Question
+ A researcher wants AI to extract facts from a report with minimal risk of invented information. Which instruction is most helpful?
+Option A
+ "Give the most complete answer possible."
+Option B
+ "Use your best judgment when information is missing."
+Option C
+ "Separate confirmed facts, uncertainties, and missing information."
+Option D
+ "Make reasonable assumptions where needed."
+Correct Answer
+ C
+Explanation
+ One of the most effective ways to reduce hallucinations is to force AI to distinguish between supported facts, uncertainty, and information that is unavailable.</t>
+  </si>
+  <si>
+    <t>Question
+ You upload a photo of a bicycle and ask AI whether the tires appear inflated. What is the most reliable way to use the answer?
+Option A
+ Treat the answer as a guaranteed fact.
+Option B
+ Use the answer as an observation and verify important details yourself.
+Option C
+ Assume AI can detect everything not visible in the image.
+Option D
+ Trust the answer more than direct inspection.
+Correct Answer
+ B
+Explanation
+ AI can analyze visible information in an image, but it cannot guarantee accuracy or detect things that are not clearly visible.</t>
+  </si>
+  <si>
+    <t>Question
+ An AI-generated marketing plan assumes all customers use social media regularly. What is the most useful review question?
+Option A
+ "How can we make the plan longer?"
+Option B
+ "Which groups or situations might this plan overlook?"
+Option C
+ "Can we add more AI-generated content?"
+Option D
+ "Can we make the language more professional?"
+Correct Answer
+ B
+Explanation
+ A key way to identify bias is to ask who may be missing, overlooked, or underrepresented in the proposed solution.</t>
+  </si>
+  <si>
+    <t>Question
+ After testing the same prompt in four AI assistants, what is the best way to decide which one performed best?
+Option A
+ Pick the answer that sounds most confident.
+Option B
+ Choose the assistant with the most famous brand.
+Option C
+ Evaluate each result using the same predefined criteria.
+Option D
+ Select the longest response.
+Correct Answer
+ C
+Explanation
+ The challenge is about comparing outputs fairly. Using the same evaluation criteria for every assistant is the only reliable way to identify which result best fits the task.</t>
+  </si>
+  <si>
+    <t>Question
+ A student asks AI: "Help me with my presentation." The response is too generic to be useful. What is the most effective improvement?
+Option A
+ Make the prompt longer without adding details.
+Option B
+ Add the specific task, context, and desired outcome.
+Option C
+ Ask AI to be more intelligent.
+Option D
+ Use more technical vocabulary.
+Correct Answer
+ B
+Explanation
+ A useful prompt makes the task and desired result clear. Adding relevant context and defining the outcome reduces guessing and produces a more useful response.</t>
+  </si>
+  <si>
+    <t>Question
+ A manager wants AI to create onboarding material for new employees. Which element is missing from this prompt: "Create onboarding material"?
+Option A
+ A task
+Option B
+ Context, requirements, and output expectations
+Option C
+ A verb
+Option D
+ Proper grammar
+Correct Answer
+ B
+Explanation
+ The task is present, but AI still lacks context, requirements, and information about the desired output format.</t>
+  </si>
+  <si>
+    <t>Question
+ Which instruction contains the clearest task?
+Option A
+ I have lots of customer feedback and I'm not sure what to do with it.
+Option B
+ Can you help me understand these comments?
+Option C
+ Identify the five most common themes in this customer feedback.
+Option D
+ Let's discuss customer opinions.
+Correct Answer
+ C
+Explanation
+ A clear task uses a specific action verb and states exactly what AI should do with the material provided.</t>
+  </si>
+  <si>
+    <t>Question
+ A project deadline has been moved back by one week. You want to inform your team without changing the facts. What should tone influence?
+Option A
+ How the message feels.
+Option B
+ The new deadline date.
+Option C
+ The project scope.
+Option D
+ The factual information being communicated.
+Correct Answer
+ A
+Explanation
+ Tone affects how information is delivered and perceived. The facts themselves should remain unchanged.</t>
+  </si>
+  <si>
+    <t>Question
+ A team leader needs employees to complete several preparation tasks before a workshop. Which output format is most useful?
+Option A
+ A long paragraph.
+Option B
+ A checklist.
+Option C
+ A descriptive essay.
+Option D
+ A timeline of company history.
+Correct Answer
+ B
+Explanation
+ The best format depends on the next action. A checklist is ideal when people need to complete and track specific tasks.</t>
+  </si>
+  <si>
+    <t>Question
+ You are comparing three online courses. What should you do before asking AI to build a comparison table?
+Option A
+ Choose the course that looks best.
+Option B
+ Decide which criteria matter for your decision.
+Option C
+ Ask AI for the table and decide later.
+Option D
+ Focus only on the course price.
+Correct Answer
+ B
+Explanation
+ A useful table is built around the criteria that matter to the decision. Without clear criteria, the comparison may not help you choose.</t>
+  </si>
+  <si>
+    <t>Question
+ You ask AI to suggest activities for a team event. The budget is limited and the event must be indoors. What is the best way to improve the prompt?
+Option A
+ Ask for more creative ideas.
+Option B
+ Tell AI to make the answer longer.
+Option C
+ Add the budget and indoor-only requirements as constraints.
+Option D
+ Ask AI to choose the most popular activity.
+Correct Answer
+ C
+Explanation
+ Constraints help prevent unusable suggestions. They define the boundaries that any acceptable solution must respect.</t>
+  </si>
+  <si>
+    <t>Question
+ An AI keeps formatting product descriptions incorrectly. What is the most effective next step?
+Option A
+ Ask AI to try harder.
+Option B
+ Provide an example showing the desired format.
+Option C
+ Use a longer prompt without examples.
+Option D
+ Generate more random outputs.
+Correct Answer
+ B
+Explanation
+ Examples help AI understand patterns and expectations. If instructions alone are unclear, a well-chosen example often improves results significantly.</t>
+  </si>
+  <si>
+    <t>Question
+ You paste a company policy into AI and want it summarized. What is the safest prompt structure?
+Option A
+ Mix your instructions directly inside the policy text.
+Option B
+ Paste the policy first and hope AI understands the task.
+Option C
+ Clearly separate the task instructions from the source material using labels.
+Option D
+ Remove all formatting and send everything together.
+Correct Answer
+ C
+Explanation
+ Separating instructions from source material reduces confusion and makes it clear what AI should do versus what content it should analyze.</t>
+  </si>
+  <si>
+    <t>Question
+ You upload a 30-page document and ask AI, "Analyze this." Why might the result be disappointing?
+Option A
+ The document is too long to read.
+Option B
+ The question does not specify what information is needed.
+Option C
+ AI cannot work with documents.
+Option D
+ Documents should always be summarized first.
+Correct Answer
+ B
+Explanation
+ A document alone does not define the task. A focused question helps AI identify which parts of the document matter.</t>
+  </si>
+  <si>
+    <t>Question
+ You want AI to help plan a personal learning project, but you are unsure what information it needs. What is the best approach?
+Option A
+ Ask AI for a complete plan immediately.
+Option B
+ Provide as many random details as possible.
+Option C
+ Ask AI to ask clarifying questions before creating the plan.
+Option D
+ Use a different AI tool.
+Correct Answer
+ C
+Explanation
+ For open-ended tasks, AI can build a better solution if it first collects the information that will influence the outcome.</t>
+  </si>
+  <si>
+    <t>Question
+ AI gives advice that is correct but too general to use. Which follow-up is most appropriate?
+Option A
+ "Make this more specific."
+Option B
+ "Write more."
+Option C
+ "Repeat the answer."
+Option D
+ "Make the language fancier."
+Correct Answer
+ A
+Explanation
+ The lesson teaches matching the follow-up to the weakness. Generic advice is improved through specificity.</t>
+  </si>
+  <si>
+    <t>Question
+ AI recommends launching a new product in June and explains its reasoning. What should you do next?
+Option A
+ Accept the recommendation because AI provided an explanation.
+Option B
+ Check the key assumptions that the recommendation depends on.
+Option C
+ Ignore the reasoning and focus only on the conclusion.
+Option D
+ Ask AI to make the explanation longer.
+Correct Answer
+ B
+Explanation
+ Reasoning helps reveal assumptions and decision criteria, but it is not proof that the conclusion is correct. Important assumptions should be verified.</t>
+  </si>
+  <si>
+    <t>Question
+ A prompt consistently produces irrelevant answers. What should you do first?
+Option A
+ Make the prompt dramatically longer.
+Option B
+ Identify the main weakness before changing anything.
+Option C
+ Switch to a different AI assistant.
+Option D
+ Add multiple new instructions at the same time.
+Correct Answer
+ B
+Explanation
+ Prompt improvement starts with diagnosis. Understanding why the prompt fails helps target the real problem instead of making random changes.</t>
+  </si>
+  <si>
+    <t>Question
+ Nina wants AI to help her prepare for a first meeting with a new supplier. Which prompt is most likely to produce a useful result?
+Option A
+ Create a five-point preparation checklist for a first supplier meeting, including topics to discuss and questions to ask.
+Option B
+ Find information about preparing for supplier meetings and show Nina several relevant sources to review.
+Option C
+ Explain what normally happens during supplier meetings and describe the responsibilities of each participant.
+Option D
+ List common questions about suppliers, business meetings, contracts, prices, delivery schedules, and professional communication.
+Correct Answer
+ A
+Explanation
+ Option A gives AI a clear task, relevant context, and a defined output. Option B could provide helpful information, but it does not directly ask AI to create the practical preparation tool Nina needs.</t>
+  </si>
+  <si>
+    <t>Question
+ Daniel asks AI to improve an email declining a colleague’s request. What should he check before sending the rewritten version?
+Option A
+ Whether the email uses more formal vocabulary than the version he originally wrote.
+Option B
+ Whether the meaning, relevant details, and intended tone still reflect what he wants to communicate.
+Option C
+ Whether the AI has expanded the email enough to make the response appear more thoughtful.
+Option D
+ Whether the wording is sufficiently different from his original draft to justify using AI.
+Correct Answer
+ B
+Explanation
+ Daniel remains responsible for the final message. He should verify that the rewrite preserves his meaning, includes the correct details, and uses an appropriate tone. More formal or elaborate language does not necessarily make an email better.</t>
+  </si>
+  <si>
+    <t>Question
+ A team member needs AI assistance with information stored inside an approved workplace platform. What should guide the choice of assistant?
+Option A
+ The assistant’s public popularity and the number of people who use it worldwide.
+Option B
+ The assistant’s ability to produce detailed answers without requiring much task-specific context.
+Option C
+ The assistant’s suitability for the task and its approved access to the relevant workplace information.
+Option D
+ The assistant’s general reputation for being better at every type of professional activity.
+Correct Answer
+ C
+Explanation
+ The appropriate assistant depends on the task, approved access, and available integrations. An assistant may be powerful in general but still be unsuitable if it cannot securely access the information required.</t>
+  </si>
+  <si>
+    <t>Question
+ Leo understands basic budgeting but is unfamiliar with cash-flow forecasting. Which request gives AI the clearest guidance?
+Option A
+ Explain cash-flow forecasting using the most technically complete financial definition available.
+Option B
+ Provide a detailed overview of cash-flow forecasting and include all standard accounting terminology.
+Option C
+ Describe cash-flow forecasting and let the AI decide what level of knowledge Leo probably has.
+Option D
+ Explain cash-flow forecasting to someone who understands basic budgets, using a simple example and limited jargon.
+Correct Answer
+ D
+Explanation
+ Option D states Leo’s existing knowledge and specifies how the explanation should be presented. Option B may be accurate, but it could still be too technical because it does not adapt the explanation to the learner.</t>
+  </si>
+  <si>
+    <t>Question
+ Priya receives a long report but only needs information affecting next quarter’s project plan. What should she ask AI to do?
+Option A
+ Shorten the entire report while preserving approximately the same emphasis across every section.
+Option B
+ Summarize the report’s main findings, deadlines, dependencies, and risks affecting next quarter’s project plan.
+Option C
+ Rewrite the complete report in simpler language so that every original point remains included.
+Option D
+ Create a general executive summary covering the report’s background, methodology, findings, and conclusion.
+Correct Answer
+ B
+Explanation
+ A focused summary should reflect the reader’s purpose. Option B identifies the specific information Priya needs. Option D could produce a useful general summary, but it may give too much attention to sections that do not affect the project plan.</t>
+  </si>
+  <si>
+    <t>Question
+ Marcus is comparing two training platforms. Cost matters, but accessibility and reporting are essential. Which request is best?
+Option A
+ Compare the platforms based on cost, accessibility, and reporting, then recommend one using accessibility and reporting as essential criteria.
+Option B
+ List the general advantages and disadvantages of both platforms and recommend whichever has more advantages overall.
+Option C
+ Compare the main features of both platforms and identify which one appears to offer the greatest functionality.
+Option D
+ Recommend the less expensive platform unless the other platform offers several additional features for administrators.
+Correct Answer
+ A
+Explanation
+ Option A makes the decision criteria and priorities explicit, allowing AI to produce a recommendation that reflects Marcus’s actual needs. Option C compares functionality but does not account for which criteria are essential.</t>
+  </si>
+  <si>
+    <t>Question
+ Sofia has notes containing decisions, unfinished tasks, deadlines, and background comments. What is the most useful instruction?
+Option A
+ Rewrite the notes as a polished summary and remove details that appear repetitive or unimportant.
+Option B
+ Sort every sentence by topic and preserve the wording exactly as it appears in the notes.
+Option C
+ Create a chronological account of the discussion and highlight statements that mention future activities.
+Option D
+ Organize the notes into decisions, action items, owners, deadlines, and unresolved questions without inventing missing details.
+Correct Answer
+ D
+Explanation
+ Option D defines useful categories and prevents AI from filling gaps with assumptions. Option A may improve readability, but removing information based on perceived importance could hide an incomplete task or unresolved issue.</t>
+  </si>
+  <si>
+    <t>Question
+ An AI assistant writes a convincing response to an employee facing a difficult decision. What does this demonstrate?
+Option A
+ The AI recognizes language patterns and generates an appropriate response without personally understanding the situation.
+Option B
+ The AI understands the employee’s circumstances because its response reflects relevant human experience.
+Option C
+ The AI forms a reliable personal judgment by combining patterns with awareness of the employee’s needs.
+Option D
+ The AI experiences a limited form of empathy when it produces language suited to an emotional situation.
+Correct Answer
+ A
+Explanation
+ AI can generate convincing and contextually appropriate language by recognizing patterns. This does not mean it possesses personal understanding, experience, judgment, or emotion.</t>
+  </si>
+  <si>
+    <t>Question
+ AI drafts a request to cancel a subscription and provides the correct customer-service address. What should the user do next?
+Option A
+ Assume the cancellation has started because the AI identified the correct contact channel.
+Option B
+ Wait for the company to send confirmation because the request has already been prepared.
+Option C
+ Send the request through the appropriate channel and verify that the company confirms the cancellation.
+Option D
+ Ask the AI to confirm whether the company has updated the subscription in its internal system.
+Correct Answer
+ C
+Explanation
+ Generating a message and identifying a contact channel are not the same as completing the action. The user must submit the request and verify the outcome. Option D would only work if the AI had explicit access to the company’s system.</t>
+  </si>
+  <si>
+    <t>Question
+ Lena wants AI to categorize support cases. Her file contains customer names, contact details, case descriptions, and reference numbers. What should she do?
+Option A
+ Upload only the most recent cases because a smaller file automatically removes the privacy risk.
+Option B
+ Keep the reference numbers but remove names, because internal identifiers do not reveal customer information.
+Option C
+ Replace the names with placeholders while retaining all other fields so the original context remains complete.
+Option D
+ Remove unnecessary personal details, replace identifiers with placeholders, and use only an approved AI service.
+Correct Answer
+ D
+Explanation
+ The safest approach combines data minimization, anonymization, and compliance with approved-tool policies. Replacing names alone may not be sufficient if contact details or reference numbers can still identify customers.</t>
+  </si>
+  <si>
+    <t>Question
+ Maya uses a free AI assistant several times a week. She is considering upgrading because the paid plan includes more features. What should she do first?
+Option A
+ Compare the number of features in each plan and choose the version offering the greatest overall capability.
+Option B
+ List her recurring tasks and test whether limitations in the free plan are preventing valuable work from being completed.
+Option C
+ Upgrade for one month and explore the premium features, even if she has not identified a specific need.
+Option D
+ Estimate how frequently she might use AI in the future and select a plan based on that potential usage.
+Correct Answer
+ B
+Explanation
+ A paid option is worthwhile when it removes a verified limitation affecting useful, recurring work. Option A provides a broader comparison, but more features do not automatically mean more value for Maya’s actual tasks.</t>
+  </si>
+  <si>
+    <t>Question
+ Ravi needs to create an original illustration for a presentation based on a detailed visual description. Which tool category is the most appropriate starting point?
+Option A
+ A conversational assistant designed primarily to explain topics and develop written ideas.
+Option B
+ A connected research tool designed to find current information and provide external sources.
+Option C
+ An AI image-generation tool designed to produce visuals from a written description.
+Option D
+ An AI feature inside a spreadsheet designed to organize and analyze structured data.
+Correct Answer
+ C
+Explanation
+ The desired output is an original visual, so an image-generation tool is the most direct match. A conversational assistant might help improve the description, but it may not be the appropriate tool for producing the final illustration.</t>
+  </si>
+  <si>
+    <t>Question
+ Elena writes similar weekly project updates using different notes each time. What would make her prompt genuinely reusable?
+Option A
+ A stable instruction with placeholders for changing details such as achievements, risks, decisions, and next steps.
+Option B
+ A completed update containing this week’s information that she can ask AI to rewrite whenever necessary.
+Option C
+ A detailed instruction covering every possible project situation she might encounter during the year.
+Option D
+ A short request asking AI to create a professional project update from whatever information she provides.
+Correct Answer
+ A
+Explanation
+ A reusable prompt preserves the recurring task, structure, and expectations while using placeholders for information that changes. Option D is reusable in a basic sense, but it does not provide enough structure to produce consistent weekly outputs.</t>
+  </si>
+  <si>
+    <t>Question
+ During one day, Hugo uses AI to summarize a policy, organize notes, improve an email, compare two services, and explain a technical term. What best demonstrates effective use?
+Option A
+ Completing all five activities in one continuous conversation so that the AI remembers the full working context.
+Option B
+ Using the same prompt structure for every activity to make the results easier to compare afterward.
+Option C
+ Selecting the most powerful available assistant and allowing it to determine the best output for each activity.
+Option D
+ Giving each activity its own clear request, relevant context, desired output, and final human review.
+Correct Answer
+ D
+Explanation
+ The five activities have different goals, so each requires an appropriately defined request and a review of the result. Option A might seem convenient, but combining unrelated tasks in one conversation can create unnecessary context and confusion.</t>
+  </si>
+  <si>
+    <t>Question
+ A designer asks AI to create a slogan containing exactly 24 characters, including spaces. What is the most reliable approach?
+Option A
+ Ask AI to produce the slogan and trust the character count when the response appears to fit.
+Option B
+ Generate candidate slogans with AI, then verify the exact character count using a dedicated counting method.
+Option C
+ Ask AI to separate every character with a space before calculating the final total itself.
+Option D
+ Request several slogans of approximately the correct length and choose the shortest available option.
+Correct Answer
+ B
+Explanation
+ AI processes text in tokens rather than consistently tracking individual characters, so exact counts should be verified with a suitable counting method. Option C may encourage more careful processing, but it still relies on AI for a task it may perform inconsistently.</t>
+  </si>
+  <si>
+    <t>Question
+ Omar needs to calculate the final cost of an order using quantities, unit prices, discounts, and tax. The result will be used for payment approval. What should he do?
+Option A
+ Ask AI to calculate the total twice and accept the result if both responses are identical.
+Option B
+ Ask AI to explain the calculation and approve the result if the reasoning appears logically structured.
+Option C
+ Use AI to estimate the result, then manually adjust any figures that appear unusual.
+Option D
+ Use a calculator or spreadsheet for the calculation and use AI only to explain or review the method.
+Correct Answer
+ D
+Explanation
+ An important calculation should be performed with a reliable calculation tool. AI can help explain the formula or review the process, but a plausible explanation does not guarantee numerical accuracy. Repeating the same AI calculation can reproduce the same error.</t>
+  </si>
+  <si>
+    <t>Question
+ After a long conversation, AI keeps applying an outdated requirement that the team removed earlier. What is the best next step?
+Option A
+ Start a new conversation with a concise summary of the current objective, valid decisions, and remaining requirements.
+Option B
+ Continue in the same conversation and repeat the updated requirement more strongly in every new message.
+Option C
+ Delete individual messages containing the old requirement while preserving the rest of the conversation.
+Option D
+ Ask AI to review the entire conversation and independently decide which instructions should still apply.
+Correct Answer
+ A
+Explanation
+ A clean restart removes accumulated and conflicting context while preserving the essential progress in a concise handover. Option D still requires AI to interpret a long, contradictory history, which is the source of the problem.</t>
+  </si>
+  <si>
+    <t>Question
+ A manager asks AI about a regulation that changed recently. The assistant provides a confident answer but does not identify a current source. How should the answer be treated?
+Option A
+ As reliable if the explanation is detailed and uses terminology commonly found in regulatory documents.
+Option B
+ As probably current because major regulatory changes are normally included in AI systems quickly.
+Option C
+ As a useful starting point that must be checked against an authoritative and up-to-date source.
+Option D
+ As incorrect unless the AI can state the exact date on which its training data was collected.
+Correct Answer
+ C
+Explanation
+ The answer may rely on stored knowledge that predates the change, so the current rule must be verified using an authoritative source. Option D is too absolute because the answer is not automatically wrong, but it is not sufficient for a current regulatory decision.</t>
+  </si>
+  <si>
+    <t>Question
+ Two AI assistants answer a question about an announcement published this morning. One provides dated links, while the other provides a response without sources. What can the user reasonably conclude?
+Option A
+ The answer with links is automatically correct because connected AI only uses verified information.
+Option B
+ The answer without links is incorrect because stored model knowledge cannot contain any useful context.
+Option C
+ Both assistants used live information, but only one displayed the sources it selected.
+Option D
+ The linked answer appears to use current external information, but its sources and claims still require review.
+Correct Answer
+ D
+Explanation
+ Dated links indicate that the first assistant appears to be using connected information, but source access does not guarantee that the answer is accurate or well supported. Option A overlooks the need to evaluate the sources and confirm that they support the claims.</t>
+  </si>
+  <si>
+    <t>Question
+ A communications team uses the same prompt to generate a standard notice, but the wording and structure change between attempts. They need greater consistency. What should they do?
+Option A
+ Generate several versions each time and choose the one that appears closest to the previous notice.
+Option B
+ Define the required structure, fixed information, tone, and evaluation criteria more explicitly in the prompt.
+Option C
+ Continue using the original prompt because variation is unavoidable and cannot be meaningfully reduced.
+Option D
+ Select the longest generated version because it is more likely to include all the required information.
+Correct Answer
+ B
+Explanation
+ Variation is normal, but clearer constraints can reduce unwanted differences by defining what must remain stable. Option A manages the variation after generation, while option B addresses the cause and creates a more repeatable process.</t>
+  </si>
+  <si>
+    <t>Question
+ Lucas needs AI to reformat a short list and later evaluate a proposal involving budget limits, deadlines, and competing priorities. Which approach is most appropriate?
+Option A
+ Use a reasoning-focused model for both tasks because additional processing generally produces a more reliable result.
+Option B
+ Use a fast model for reformatting and a reasoning-focused model for evaluating the connected constraints.
+Option C
+ Use a fast model for both tasks, then request longer answers if the evaluation lacks sufficient detail.
+Option D
+ Use a reasoning-focused model for reformatting and a fast model for evaluating the proposal’s constraints.
+Correct Answer
+ B
+Explanation
+ The simple formatting task mainly requires speed, while the proposal requires consideration of several connected factors. Option A could complete both tasks, but it uses additional processing where it is unlikely to provide meaningful value.</t>
+  </si>
+  <si>
+    <t>Question
+ Four AI assistants receive the same request but produce responses with different structures, detail, and source usage. How should the team compare them fairly?
+Option A
+ Repeat the request until every assistant produces an answer with approximately the same structure and length.
+Option B
+ Select the response containing the most information because completeness is the most objective measure of quality.
+Option C
+ Give each assistant the same input and evaluate the outputs against criteria connected to the task.
+Option D
+ Choose the assistant whose first response requires the fewest changes, regardless of the task’s requirements.
+Correct Answer
+ C
+Explanation
+ A fair comparison requires consistent input and predefined evaluation criteria, such as accuracy, relevance, structure, or source quality. Option D could be one useful observation, but it is insufficient unless the required changes are assessed against the actual task criteria.</t>
+  </si>
+  <si>
+    <t>Question
+ A software platform releases an AI model with a higher version number than the model currently used by a team. What can the team safely conclude?
+Option A
+ The label identifies a different version, but its suitability must be verified through documentation and task-specific testing.
+Option B
+ The newer version will perform better because version numbers normally reflect overall improvement across tasks.
+Option C
+ The newer version should replace the existing one unless the provider explicitly describes it as experimental.
+Option D
+ The higher number indicates greater capability, although the practical difference may be small for familiar tasks.
+Correct Answer
+ A
+Explanation
+ A model name or version helps identify the product, but it does not guarantee better performance for every use case. Option D may sound reasonable, but even greater general capability cannot be assumed from the version number alone.</t>
+  </si>
+  <si>
+    <t>Question
+ An assistant refers to a preference mentioned in an earlier conversation. Before relying on this behaviour, what should the user determine?
+Option A
+ Whether the earlier conversation remains visible in the user’s chat history and can still be opened manually.
+Option B
+ Whether the preference is present in the current conversation, stored by an optional memory feature, or supplied another way.
+Option C
+ Whether the assistant has reviewed every previous conversation associated with the user’s account.
+Option D
+ Whether keeping the original conversation open allows its information to become available in all future chats.
+Correct Answer
+ B
+Explanation
+ Conversation context, visible chat history, and optional memory are different mechanisms. The assistant’s reference does not prove that it can freely review every earlier conversation. Seeing an old chat in the interface also does not mean its content is automatically active in a new one.</t>
+  </si>
+  <si>
+    <t>Question
+ A team wants an assistant for recurring spreadsheet analysis. Two models make similar general capability claims. What is the best selection method?
+Option A
+ Choose the model with the broadest feature list because it is more likely to handle complex spreadsheet tasks.
+Option B
+ Compare public demonstrations and select the model receiving the strongest reviews for professional data analysis.
+Option C
+ Use both models for several unrelated activities and select the one that performs best across all of them.
+Option D
+ Test both with representative spreadsheet tasks and evaluate correctness, consistency, and usefulness using the same criteria.
+Correct Answer
+ D
+Explanation
+ Models should be evaluated using realistic examples from the intended work and consistent criteria. Public reviews can provide context, but they may not reflect the team’s files, tasks, or quality requirements.</t>
+  </si>
+  <si>
+    <t>Question
+ A user encounters an unfamiliar warning while configuring an application. How should they use a screenshot to investigate the problem?
+Option A
+ Share the complete screen so the AI can independently decide which visible information is relevant to the warning.
+Option B
+ Describe the application and ask AI to list every warning that could appear during configuration.
+Option C
+ Crop the image to the warning and provide it without explanation so that the visual remains the primary evidence.
+Option D
+ Remove sensitive details, share the relevant area, and explain what action produced the warning and what was expected.
+Correct Answer
+ D
+Explanation
+ The screenshot supplies visual evidence, while the surrounding context helps AI interpret what happened. Option C protects focus, but the image alone may not reveal the action, expected result, or conditions that produced the warning.</t>
+  </si>
+  <si>
+    <t>Question
+ A manager asks AI to “create a project update” and receives an unsuitable result. Which revision adds the most useful specificity?
+Option A
+ Create a professional project update that is clear, polished, informative, concise, and appropriate for business readers.
+Option B
+ Create a project update using the notes provided, with progress, current risks, decisions needed, and next steps for the steering committee.
+Option C
+ Create a detailed project update that includes all important information and avoids anything the readers may find unnecessary.
+Option D
+ Create a project update similar to the reports normally shared by experienced project managers with senior stakeholders.
+Correct Answer
+ B
+Explanation
+ Option B defines the source material, required sections, and intended audience. Option A provides useful quality words, but terms such as “professional” and “clear” do not specify what information the output must contain.</t>
+  </si>
+  <si>
+    <t>Question
+ Aisha asks AI to recommend activities for a team workshop. Which additional context would most significantly improve the recommendations?
+Option A
+ The group size, workshop objective, available time, location constraints, and participants’ level of familiarity.
+Option B
+ The preferred writing style, number of suggestions, and format in which the activities should be presented.
+Option C
+ A request for practical, engaging, original activities that can create a positive experience for everyone.
+Option D
+ Examples of popular workshop activities used by other teams in a variety of professional situations.
+Correct Answer
+ A
+Explanation
+ The appropriate activities depend on the purpose, participants, time, and practical constraints. Option B would improve the presentation of the answer, but it would not give AI enough situational information to choose suitable activities.</t>
+  </si>
+  <si>
+    <t>Question
+ A specialist wants AI to explain a new data policy to colleagues who use company systems but have no compliance background. Which instruction is most effective?
+Option A
+ Explain the policy accurately and include the terminology used by compliance specialists in the official documentation.
+Option B
+ Explain the policy to general employees, concentrating on the information that most people will probably find useful.
+Option C
+ Explain the policy to non-specialists who use company systems, focusing on required actions and using limited technical language.
+Option D
+ Explain the complete policy in simple language and allow readers to decide which requirements apply to their work.
+Correct Answer
+ C
+Explanation
+ Option C identifies the audience’s knowledge, working context, and practical need. Option B is directionally useful but remains broad and does not explain what the audience should be able to do after reading the content.</t>
+  </si>
+  <si>
+    <t>Question
+ A company wants AI to review instructions before they are added to a customer self-service portal. Which role adds the most useful perspective?
+Option A
+ Act as an experienced communication professional and make the instructions sound highly polished and authoritative.
+Option B
+ Act as a customer-support editor and identify unclear steps, assumed knowledge, and terms customers may not understand.
+Option C
+ Act as a leading expert in digital customer experience and produce the best possible version of the instructions.
+Option D
+ Act as a demanding customer and rewrite every instruction that does not immediately appear simple and engaging.
+Correct Answer
+ B
+Explanation
+ The customer-support editor role introduces a relevant perspective and specific review responsibilities. Option A could improve the writing style, but it does not direct AI to examine usability, hidden assumptions, or customer understanding.</t>
+  </si>
+  <si>
+    <t>Question
+ Marta needs a project update for a dashboard where readers scan information quickly. Which instruction provides the most useful length control?
+Option A
+ Summarize the project clearly and keep the update short enough for senior stakeholders to review quickly.
+Option B
+ Write three bullets of no more than 15 words each, covering progress, the main risk, and the next milestone.
+Option C
+ Create a concise project update containing only the information that readers are likely to consider essential.
+Option D
+ Reduce the project notes to their most important points while preserving sufficient context for decision-making.
+Correct Answer
+ B
+Explanation
+ Option B connects a measurable limit to the destination and identifies the information that must remain. Option A describes the intended experience, but “short enough” can be interpreted differently and may produce inconsistent results.</t>
+  </si>
+  <si>
+    <t>Question
+ AI produces a useful onboarding guide, but the final section is too technical for new employees. What should the user request?
+Option A
+ Create a new onboarding guide using simpler language and the same source information as the previous version.
+Option B
+ Rewrite the complete guide for new employees and preserve any information that still appears relevant.
+Option C
+ Keep the existing structure and earlier sections, but rewrite the final section in plain language for new employees.
+Option D
+ Generate several alternatives for the guide and select the version with the least technical language overall.
+Correct Answer
+ C
+Explanation
+ The existing guide already has a strong foundation, so the user should identify the weak section and request a focused revision while preserving the rest. Option A may solve the language issue, but restarting could unnecessarily change useful content and structure.</t>
+  </si>
+  <si>
+    <t>Question
+ An AI-generated event announcement is accurate except for the location. Which correction is most likely to preserve the valid content?
+Option A
+ The location is incorrect. Replace it with Conference Room 4B and leave the date, time, and wording unchanged.
+Option B
+ Review the announcement again because one of the event details is wrong and should be corrected.
+Option C
+ Rewrite the announcement using Conference Room 4B and confirm that all remaining information still appears accurate.
+Option D
+ Create a corrected version that fixes the location and improves any other details that may be unclear.
+Correct Answer
+ A
+Explanation
+ Option A identifies the exact error, supplies the replacement, and states what must remain unchanged. Option C includes the correction, but requesting a rewrite may cause unnecessary changes to content that is already valid.</t>
+  </si>
+  <si>
+    <t>Question
+ A team asks AI for five names for an internal knowledge platform. What should they do before selecting one?
+Option A
+ Choose the name that receives the strongest positive reaction during the team’s first discussion.
+Option B
+ Select the most original name, provided that it does not closely resemble an existing product.
+Option C
+ Ask AI to rank its suggestions and select the name it identifies as the strongest overall choice.
+Option D
+ Evaluate each name against agreed criteria such as clarity, relevance, memorability, and suitability for employees.
+Correct Answer
+ D
+Explanation
+ Predefined criteria create a consistent basis for comparing the options. Option B uses two reasonable considerations, but originality alone does not show whether a name is clear, relevant, or suitable for the intended audience.</t>
+  </si>
+  <si>
+    <t>Question
+ Nora is contacting a potential research partner for the first time. Which email approach is most likely to encourage a response?
+Option A
+ Introduce herself in detail, explain her organization’s background, and describe the complete research programme before requesting a meeting.
+Option B
+ Open with a general compliment, present several possible collaboration ideas, and ask which opportunity sounds most interesting.
+Option C
+ Describe the research challenge, attach supporting information, and invite the recipient to review it when convenient.
+Option D
+ State the relevant connection, explain one clear reason for contacting them, and suggest a brief, specific next step.
+Correct Answer
+ D
+Explanation
+ A strong first-contact email gives the recipient a clear reason to care and makes the response easy. Option C supplies useful context, but reviewing attached material requires more effort and does not provide a precise next step.</t>
+  </si>
+  <si>
+    <t>Question
+ Jon needs to tell a colleague that repeated late submissions are affecting the team’s work. Which message structure is most appropriate?
+Option A
+ Describe the specific pattern and its impact, ask what is causing the difficulty, and agree on a workable next step.
+Option B
+ Emphasize how frustrating the delays have been, then ask the colleague to make future submissions a priority.
+Option C
+ Explain that the team expects deadlines to be respected and request confirmation that the issue will not happen again.
+Option D
+ Begin with positive feedback, mention the delays indirectly, and allow the colleague to suggest whether a change is necessary.
+Correct Answer
+ A
+Explanation
+ Option A is direct about the issue and its impact while creating space to understand the cause and agree on a solution. Option C communicates the expectation clearly, but it assumes commitment alone will solve the problem without exploring what is causing it.</t>
+  </si>
+  <si>
+    <t>Question
+ A meeting note says, “The new training material needs review before next month’s pilot.” What should AI do when converting this into an action item?
+Option A
+ Assign the review to the meeting organizer and set the deadline for the final working day before the pilot.
+Option B
+ Create the task, select the most relevant attendee as owner, and calculate a reasonable review deadline.
+Option C
+ Record the review as an action item and mark the owner and exact deadline as not specified.
+Option D
+ Keep the statement under meeting notes until the team confirms that someone has accepted responsibility.
+Correct Answer
+ C
+Explanation
+ The note identifies a required action but does not provide an owner or precise deadline. AI should preserve the task while making the missing information visible. Option D avoids inventing details, but it also fails to surface a clear action that requires follow-up.</t>
+  </si>
+  <si>
+    <t>Question
+ A consultant needs to explain why a data migration requires an additional validation stage. Which approach is most client-focused?
+Option A
+ Describe the validation architecture and the technical checks performed across the migration environments.
+Option B
+ Explain that the validation stage reduces the risk of missing or incorrect records, what it means for timing, and whether the client must act.
+Option C
+ Provide a complete description of the migration process so the client understands where validation fits within the methodology.
+Option D
+ Summarize the technical benefits of validation and demonstrate how the additional stage follows industry best practices.
+Correct Answer
+ B
+Explanation
+ Option B focuses on the client’s real concerns: why the step matters, its practical effect, and any required action. Option C provides broader understanding, but it may introduce process detail that does not help the client make a decision.</t>
+  </si>
+  <si>
+    <t>Question
+ While travelling, Diego needs AI to prepare a quick handover from his notes. Which mobile prompt is most effective?
+Option A
+ Help me prepare a handover from these notes and ensure that the result is complete and professionally written.
+Option B
+ Review these notes and identify the information another colleague would need to continue the work successfully.
+Option C
+ Turn these notes into a short handover with completed work, open actions, owners, and immediate next steps.
+Option D
+ Create a clear handover document from the information below and organize it using an appropriate professional structure.
+Correct Answer
+ C
+Explanation
+ Option C remains compact while defining the task, expected length, and required structure. Option B gives AI a relevant objective, but it does not specify the output format, making the result less predictable and immediately usable.</t>
+  </si>
+  <si>
+    <t>Question
+ A consulting team uses AI every month to transform project notes into a client update. The results vary depending on who runs the task. Which change would most improve reliability?
+Option A
+ Create a standard process defining required inputs, transformation steps, output sections, and a final human review.
+Option B
+ Keep the current approach but provide users with several examples of previously approved client updates.
+Option C
+ Allow each user to adapt the prompt while requiring every final update to follow the same visual template.
+Option D
+ Use one detailed master prompt containing instructions for every project situation the team might encounter.
+Correct Answer
+ A
+Explanation
+ A repeatable system controls the full process, including inputs, instructions, output, and review. Option B could improve consistency, but examples alone do not define how missing information, changing inputs, or quality checks should be handled.</t>
+  </si>
+  <si>
+    <t>Question
+ A team needs AI to convert technical release notes into a short update for account managers. Which instruction applies RTF most effectively?
+Option A
+ Act as a technical writer and improve these release notes so account managers can understand the changes.
+Option B
+ Summarize these release notes for account managers and emphasize changes that could affect customer conversations.
+Option C
+ Act as a product communications specialist. Convert the release notes into five customer-impact bullets with a short heading.
+Option D
+ Review the release notes, identify important changes, and present the information in a concise professional format.
+Correct Answer
+ C
+Explanation
+ Option C clearly defines the role, task, and output format. Option B is also a useful prompt, but it does not explicitly control the format, so the resulting structure may vary between runs.</t>
+  </si>
+  <si>
+    <t>Question
+ A public library wants AI to recommend ways to increase attendance at weekday workshops. Which prompt makes the strongest use of RACE?
+Option A
+ Act as a community-programme adviser and recommend practical ways to increase attendance at our weekday workshops.
+Option B
+ Recommend six promotional ideas for weekday workshops and prioritize the options requiring the fewest resources.
+Option C
+ Review our workshop attendance problem, consider local community needs, and suggest improvements suitable for a library.
+Option D
+ Act as a community-programme adviser. Recommend improvements for free weekday workshops attended mainly by retirees. Keep the current budget and prioritize actions possible within one month.
+Correct Answer
+ D
+Explanation
+ Option D defines a relevant role, the required action, material context, and clear expectations. Option A contains a role and action, but it lacks the operational constraints needed to make the recommendations suitable for this library.</t>
+  </si>
+  <si>
+    <t>Question
+ A user has two tasks: convert interview notes into a fixed template, and design an onboarding process for contractors handling confidential information. Which framework choice is most appropriate?
+Option A
+ Use RTF for the notes and RACE for the onboarding process because the second task depends on context and constraints.
+Option B
+ Use RACE for both tasks because additional context generally improves the reliability of any professional output.
+Option C
+ Use RTF for both tasks because each one ultimately needs a clearly defined format and deliverable.
+Option D
+ Use RACE for the notes and RTF for onboarding because process design benefits from a simpler instruction structure.
+Correct Answer
+ A
+Explanation
+ The note-conversion task is contained and mainly requires control over the task and format. The onboarding process depends on operational context, confidentiality requirements, and success expectations, making RACE more appropriate. Using RACE for both could work, but it would add unnecessary structure to the simpler task.</t>
+  </si>
+  <si>
+    <t>Question
+ AI recommends how a department should divide a limited training budget across four teams. Why might requesting intermediate steps improve the review?
+Option A
+ It forces the AI to use a single calculation method, reducing the possibility of receiving alternative recommendations.
+Option B
+ It reveals the criteria, assumptions, and trade-offs connecting the available information to the proposed allocation.
+Option C
+ It makes the recommendation more detailed, which gives decision-makers more evidence that the conclusion is reliable.
+Option D
+ It ensures every numerical operation is correct because the calculation becomes visible to the decision-makers.
+Correct Answer
+ B
+Explanation
+ Intermediate steps make the decision path inspectable, allowing reviewers to challenge assumptions and trade-offs. Option C confuses detail with reliability. A longer explanation can still contain weak assumptions or incorrect reasoning.</t>
+  </si>
+  <si>
+    <t>Question
+ A team asks AI to research a topic, identify customer needs, design a service, create launch messaging, and prepare an implementation plan. What is the strongest reason to divide the work?
+Option A
+ Separate tasks make every output shorter, which reduces the amount of information the team must evaluate.
+Option B
+ Each stage can use a different writing style, allowing the final result to appeal to several audiences.
+Option C
+ The team can review assumptions and outputs at key points before errors influence the later stages.
+Option D
+ AI performs more reliably when every complex assignment is divided into stages of approximately equal size.
+Correct Answer
+ C
+Explanation
+ Decomposition creates review points before one weak result becomes input for subsequent work. Option A may sometimes be a benefit, but shorter outputs are not the main objective. The value comes from controlling dependencies and quality across the workflow.</t>
+  </si>
+  <si>
+    <t>Question
+ A workflow first extracts requirements from a proposal and then uses them to create an evaluation checklist. What is the most important control between the two stages?
+Option A
+ Ensure both prompts use identical terminology so the comparison between their outputs remains straightforward.
+Option B
+ Review whether the extracted requirements are complete and accurate before using them to build the checklist.
+Option C
+ Use the same AI model for both stages so the interpretation remains consistent throughout the process.
+Option D
+ Preserve the full first response as input so the second stage has access to all available background information.
+Correct Answer
+ B
+Explanation
+ The first output becomes a dependency for the second stage, so it should be reviewed before the chain continues. Option D preserves more context, but additional context cannot compensate for missing or incorrectly extracted requirements.</t>
+  </si>
+  <si>
+    <t>Question
+ During a content chain, the outline contains the correct sections but gives too much emphasis to a secondary topic. What should happen before drafting begins?
+Option A
+ Continue to the draft and correct the imbalance during the final polishing stage.
+Option B
+ Generate several drafts from the outline and select the version with the strongest overall balance.
+Option C
+ Adjust the outline’s priorities, confirm the revised structure, and then use it as the drafting input.
+Option D
+ Keep the outline unchanged but add a drafting instruction limiting the secondary topic to one paragraph.
+Correct Answer
+ C
+Explanation
+ The outline controls the draft’s structure and emphasis, so the imbalance should be corrected at that stage. Option D might reduce the immediate problem, but it leaves a known weakness in the approved input and makes the later prompt compensate for it.</t>
+  </si>
+  <si>
+    <t>Question
+ AI drafts a procedure and then reports that the result is clear and complete. How should the user make the self-critique more useful?
+Option A
+ Ask for a second critique using a more demanding tone and request stricter feedback on the procedure.
+Option B
+ Ask the AI to compare the procedure against explicit criteria and identify evidence for each weakness it finds.
+Option C
+ Ask another AI assistant to review the procedure without showing it the first assistant’s evaluation.
+Option D
+ Request several critique versions and focus on weaknesses that appear consistently across all responses.
+Correct Answer
+ B
+Explanation
+ Explicit criteria make the critique more structured and less dependent on a vague judgment of quality. Option C can provide an independent perspective, but without defined criteria the second assistant may evaluate different aspects or produce equally general feedback.</t>
+  </si>
+  <si>
+    <t>Question
+ A team uses a rubric to assess AI-generated service descriptions. One description receives high scores for clarity and tone but a low score for factual support. What is the best next step?
+Option A
+ Revise the unsupported claims using verified information, then reassess the description against the complete rubric.
+Option B
+ Keep the description because its average score remains high across the other quality dimensions.
+Option C
+ Improve the clarity and tone further so their higher scores compensate for the weaker factual support.
+Option D
+ Adjust the weighting of factual support if the description is intended mainly for promotional communication.
+Correct Answer
+ A
+Explanation
+ The rubric identifies factual support as the specific weakness, so the revision should target unsupported claims and then be reassessed. A strong average cannot compensate for a critical reliability gap, particularly when customers may interpret the claims as factual.</t>
+  </si>
+  <si>
+    <t>Question
+ A team asks AI to create a client implementation guide. The first draft is polished, but it focuses on technical architecture instead of the client’s implementation journey. Which approach would best prevent this problem?
+Option A
+ Request a proposed structure, purpose for each section, and missing information before authorizing the complete draft.
+Option B
+ Generate the complete guide first, then use a client-readiness rubric to identify sections requiring substantial revision.
+Option C
+ Provide a previous implementation guide and ask AI to reproduce its organization for the new client.
+Option D
+ Request separate drafts from technical and client perspectives, then combine the strongest sections from each version.
+Correct Answer
+ A
+Explanation
+ Reviewing the plan first allows the team to correct the guide’s direction, structure, and information gaps before drafting begins. Option B introduces a useful quality check, but it identifies structural problems only after effort has already been invested in the full draft.</t>
+  </si>
+  <si>
+    <t>Question
+ A coordinator asks AI to organize supplier records, but some entries do not include delivery times. Which instruction would produce the most reliable table?
+Option A
+ Create one row per supplier and combine related operational information when separate fields contain missing values.
+Option B
+ Create one row per supplier, use a defined column for each data type, and enter “Not provided” for unavailable delivery times.
+Option C
+ Create a consistent supplier table and estimate missing delivery times from suppliers with similar locations and services.
+Option D
+ Create separate tables for complete and incomplete supplier records so that every visible row contains all required information.
+Correct Answer
+ B
+Explanation
+ A reliable table uses consistent rows and columns while keeping missing information visible. Option D avoids mixing complete and incomplete records, but separating them makes comparison harder and still does not provide a consistent representation of all suppliers.</t>
+  </si>
+  <si>
+    <t>Question
+ AI must generate transaction records that will be pasted into a spreadsheet and used for calculations. Which output specification is most appropriate?
+Option A
+ Return a formatted table with currency symbols, explanatory notes, and highlighted cells for incomplete transactions.
+Option B
+ Return comma-separated records with descriptive date labels and short explanations beside unusual amounts.
+Option C
+ Return one record per row, use a fixed column order, standardize dates, and place numbers only in numerical fields.
+Option D
+ Return a readable table and include any uncertainty inside the affected cell so that no context is lost.
+Correct Answer
+ C
+Explanation
+ Spreadsheet-ready data needs predictable columns, consistent formats, and clean numerical fields. Option D preserves context, but mixing values with explanatory text can prevent numerical fields from being calculated, filtered, or sorted correctly.</t>
+  </si>
+  <si>
+    <t>Question
+ A support team wants AI to extract information from incident reports. Its current field named “Details” contains symptoms, affected systems, business impact, and attempted fixes. What should the team do?
+Option A
+ Keep the Details field but provide examples showing how the different types of information should be ordered.
+Option B
+ Allow AI to create additional fields whenever an incident contains information that does not fit the standard structure.
+Option C
+ Replace Details with a longer field definition explaining every type of information that may appear inside it.
+Option D
+ Split Details into specifically defined fields for symptoms, affected systems, business impact, and attempted fixes.
+Correct Answer
+ D
+Explanation
+ Each field should contain one clearly defined type of information. Option A may produce more orderly text, but the field would still combine several data types and create unreliable records for filtering and comparison.</t>
+  </si>
+  <si>
+    <t>Question
+ A department wants future announcements to maintain the communication style associated with a former director. Which instruction is most appropriate?
+Option A
+ Use the former director’s previous announcements as models and reproduce their distinctive phrasing wherever relevant.
+Option B
+ Use concise sentences, calm language, practical explanations, and a brief invitation to ask questions.
+Option C
+ Draft the announcement as the former director would have written it, but avoid including personal stories or opinions.
+Option D
+ Match the former director’s tone closely while adding a note explaining that AI helped prepare the announcement.
+Correct Answer
+ B
+Explanation
+ Option B describes observable communication traits without asking AI to impersonate a real person. Option D is more transparent than direct impersonation, but it still asks AI to reproduce a specific individual’s personal voice rather than applying approved general characteristics.</t>
+  </si>
+  <si>
+    <t>Question
+ A policy team wants AI to answer employee questions using an approved document. One question concerns a situation not covered in the document. How should the prompt instruct AI to respond?
+Option A
+ Use the document as the primary source, then add recognised industry practices when the document does not contain the answer.
+Option B
+ Answer from the document where possible and label any additional conclusions as reasonable interpretations rather than confirmed policy.
+Option C
+ Use only the supplied document, identify the supporting passage, and state that the answer is not provided when no support exists.
+Option D
+ Compare the document with general knowledge and present the answer that appears most consistent with the policy’s purpose.
+Correct Answer
+ C
+Explanation
+ Grounding makes the approved document the boundary of the answer and requires unsupported questions to remain visibly unresolved. Option B separates interpretation from confirmed policy, but it still allows conclusions that are not supported by the approved source.</t>
+  </si>
+  <si>
+    <t>Question
+ An AI workflow creates event listings from organizer submissions. Some records lack confirmed prices or accessibility information. Which guardrail is strongest?
+Option A
+ Use “Confirmation required” for unsupported fields and list the specific information that must be requested from the organizer.
+Option B
+ Leave unsupported fields empty and produce a separate general warning that some listings may contain incomplete information.
+Option C
+ Use likely values only when similar events from the same organizer provide a consistent pattern.
+Option D
+ Complete the supported fields and exclude any event whose submission contains information that cannot be confirmed.
+Correct Answer
+ A
+Explanation
+ Option A converts uncertainty into a visible gap and a concrete follow-up question without inventing information. Option B avoids guessing, but empty fields can be overlooked and do not explain what confirmation is needed.</t>
+  </si>
+  <si>
+    <t>Question
+ A manager has a lengthy audit report but only needs to understand issues affecting supplier onboarding. What is the most reliable review sequence?
+Option A
+ Generate an executive summary, search it for onboarding terms, and expand any summary point that appears relevant.
+Option B
+ Divide the report into equal sections, summarize each section separately, and combine every finding into one review.
+Option C
+ Search directly for supplier-related terms and extract each paragraph containing a possible onboarding reference.
+Option D
+ Map the report’s structure, select the relevant sections, analyse them separately, and combine the reviewed findings with references.
+Correct Answer
+ D
+Explanation
+ The strongest workflow first navigates the document, then selects, analyses, and combines only the relevant material. Option A is efficient, but an initial general summary may omit details that are important to the manager’s specific question.</t>
+  </si>
+  <si>
+    <t>Question
+ A product team receives a strategy document covering customers, pricing, operations, partnerships, and technology. It needs detailed guidance only on partnership risks. What should it do?
+Option A
+ Request a detailed analysis of every section so the partnership risks can be interpreted within the complete strategy.
+Option B
+ Request a concise overview of all major sections, then expand the partnership-risk section while preserving the document’s evidence boundaries.
+Option C
+ Ask AI to extract every sentence mentioning partnerships and rewrite those passages as a complete risk assessment.
+Option D
+ Request a partnership-risk analysis directly and allow AI to use other sections whenever additional context appears necessary.
+Correct Answer
+ B
+Explanation
+ A concise overview helps the team understand the whole document and deliberately select the area requiring more detail. Option C focuses on the relevant language, but simple extraction may miss risks implied by connected operational or commercial sections.</t>
+  </si>
+  <si>
+    <t>Question
+ A company is choosing between adapting its current platform and purchasing a replacement. Which request would produce the most decision-ready comparison?
+Option A
+ Compare both options against cost, implementation effort, capability gaps, and future scalability, then identify which change would reverse the recommendation.
+Option B
+ Describe the advantages and disadvantages of both options and recommend the one with the strongest overall balance.
+Option C
+ Evaluate the current platform first, then assess whether the replacement solves the weaknesses identified during that analysis.
+Option D
+ Score both options against the same criteria and recommend whichever receives the highest total numerical score.
+Correct Answer
+ A
+Explanation
+ Option A applies shared criteria, makes the trade-offs visible, and asks for a decision threshold showing when the preferred option would change. Option D introduces comparable criteria, but a total score can conceal critical trade-offs and does not reveal the condition that would reverse the recommendation.</t>
+  </si>
+  <si>
+    <t>Question
+ A company asks AI to review a proposed customer self-service portal from five professional perspectives. The responses contain useful observations but several conflicting recommendations. What should the team do next?
+Option A
+ Combine repeated concerns, preserve meaningful conflicts, and decide which trade-offs require accountable human judgment.
+Option B
+ Prioritize the perspective that identifies the largest number of risks because it provides the most comprehensive review.
+Option C
+ Ask AI to merge all recommendations into one plan that satisfies every perspective as evenly as possible.
+Option D
+ Select the recommendation supported by the majority of perspectives and treat it as the preferred expert conclusion.
+Correct Answer
+ A
+Explanation
+ Multiple perspectives broaden the review, but they are simulated viewpoints rather than independent expert approval. Repeated concerns can reveal common priorities, while genuine conflicts should remain visible for human decision-making. Option D offers a simple selection method, but majority agreement does not resolve differences in expertise, impact, or accountability.</t>
+  </si>
+  <si>
+    <t>Question
+ An AI assistant repeatedly writes internal updates using vague claims such as “excellent progress” and “significant improvements.” Which instruction would best correct the pattern?
+Option A
+ Avoid overly positive wording and use a more neutral, factual, and professional communication style throughout the update.
+Option B
+ Replace vague claims with measurable facts and remove any statement that cannot be supported by the supplied project information.
+Option C
+ Avoid wording such as “excellent progress” because it makes unsupported judgments. Instead, describe confirmed changes, results, and unresolved issues.
+Option D
+ Use previous approved updates as examples and reproduce their balance between positive developments and remaining project risks.
+Correct Answer
+ C
+Explanation
+ Option C shows the unwanted pattern, explains why it fails, and defines the acceptable replacement. Option B provides a strong positive direction, but it does not demonstrate the specific language pattern the AI should recognize and avoid.</t>
+  </si>
+  <si>
+    <t>Question
+ A coordinator wants a reusable prompt for converting event submissions into standardized listings but is unsure which rules the prompt needs. What is the strongest use of meta-prompting?
+Option A
+ Ask AI to create the most comprehensive possible prompt based on typical event-listing workflows and common professional standards.
+Option B
+ Describe the input, required fields, missing-value behaviour, and intended output, then ask AI to identify gaps and draft the prompt.
+Option C
+ Provide several event submissions and ask AI to infer the correct workflow before producing a reusable prompt automatically.
+Option D
+ Ask AI to improve the current prompt without explaining the recurring errors, required fields, or expected final structure.
+Correct Answer
+ B
+Explanation
+ Meta-prompting works best when the user defines the task, available input, expected result, and known rules before asking AI to draft the reusable instruction. Option C may reveal useful patterns, but allowing AI to infer the workflow can introduce assumptions the coordinator does not understand or approve.</t>
+  </si>
+  <si>
+    <t>Question
+ A reusable prompt correctly extracts customer names, dates, and requested services but repeatedly assigns the wrong urgency level. What is the best first debugging action?
+Option A
+ Compare the expected urgency classification with the actual output and examine the instruction or example governing that field.
+Option B
+ Add more detailed instructions for every extracted field so that the complete prompt becomes less open to interpretation.
+Option C
+ Test the prompt with a different AI model to determine whether the urgency errors are specific to the current system.
+Option D
+ Rewrite the classification section and add several new examples before testing the prompt with different customer records.
+Correct Answer
+ A
+Explanation
+ Prompt debugging begins by isolating the visible gap and identifying the element most likely to cause it. Option D may eventually help, but changing the instruction and adding several examples simultaneously would make it difficult to know which change corrected the problem.</t>
+  </si>
+  <si>
+    <t>Question
+ A prompt reliably converts standard booking requests into structured records. Which test would provide the strongest evidence that it can handle real-world variation?
+Option A
+ Process several more standard requests and confirm that each one produces the same fields and formatting.
+Option B
+ Run the same complete request repeatedly and compare whether the extracted information remains consistent.
+Option C
+ Test a longer standard request containing additional background information but no missing or conflicting fields.
+Option D
+ Test requests with a missing date, conflicting locations, multiple participants, and information outside the expected format.
+Correct Answer
+ D
+Explanation
+ Hard cases expose weaknesses that clean, predictable inputs do not reveal. Missing, conflicting, unusually structured, or multiple-value inputs test how the prompt handles uncertainty and exceptions. Option A checks consistency under normal conditions, but it does not examine where the prompt is most likely to fail.</t>
+  </si>
+  <si>
+    <t>Question
+ A revised prompt improves category classification but has not yet been tested with incomplete records. Colleagues currently rely on the previous version. What should the owner do?
+Option A
+ Replace the shared prompt but keep a private copy of the previous version in case users report new problems.
+Option B
+ Continue editing the shared prompt until it handles both standard and incomplete records without visible errors.
+Option C
+ Publish the revision as a new version, document the classification change, test it separately, and retain the working version.
+Option D
+ Keep the same prompt name and add a note explaining that the latest version may behave differently with incomplete information.
+Correct Answer
+ C
+Explanation
+ A new version should preserve the last working prompt, record what changed, and undergo testing before replacement. Option A keeps a fallback, but it exposes colleagues to an insufficiently tested revision and makes the change less controlled.</t>
+  </si>
+  <si>
+    <t>Question
+ A weekly reporting workflow receives updates from several workstreams. One update says an activity is “almost complete” but provides no approved status or completion date. How should the report handle it?
+Option A
+ Classify it as in progress and add a note that the final completion date has not yet been confirmed.
+Option B
+ Mark the status as “Update required” and identify the missing confirmation instead of interpreting “almost complete.”
+Option C
+ List it under completed work but flag the status for verification before the report is distributed externally.
+Option D
+ Exclude the activity from the report until the workstream provides a confirmed status and completion date.
+Correct Answer
+ B
+Explanation
+ A reliable report should not convert informal wording into an unsupported status. Option B makes the uncertainty visible and indicates what information is needed. Option A may appear reasonable, but it still interprets the phrase rather than preserving the source’s uncertainty.</t>
+  </si>
+  <si>
+    <t>Question
+ A candidate meets most requirements for a role but lacks direct experience with one requested platform. The candidate has used a comparable system. How should AI support the application?
+Option A
+ Describe the comparable experience accurately, explain its relevance, and keep the missing platform experience visible.
+Option B
+ Present the comparable system as equivalent because the underlying responsibilities and workflow principles are similar.
+Option C
+ Focus the application on stronger requirements and avoid mentioning the platform unless it arises during an interview.
+Option D
+ Rewrite the experience using the requested platform’s terminology while avoiding any explicit statement of direct experience.
+Correct Answer
+ A
+Explanation
+ The application can highlight transferable evidence without claiming experience the candidate does not have. Option B may make the application sound stronger, but treating comparable experience as equivalent can misrepresent the candidate’s background.</t>
+  </si>
+  <si>
+    <t>Question
+ A research brief contains well-supported findings, but the available evidence does not resolve whether the recommendation will work in the organization’s local context. What should the brief do?
+Option A
+ Make a provisional recommendation based on the available evidence and remove uncertainty that could weaken decision confidence.
+Option B
+ Expand the findings section with additional interpretation so decision-makers can reach a conclusion from the existing evidence.
+Option C
+ Move the unresolved local issues into an appendix so the main brief remains focused on actionable conclusions.
+Option D
+ Separate the supported findings from the limitation and specify which local questions require further confirmation.
+Correct Answer
+ D
+Explanation
+ A credible research brief shows where the evidence ends and which questions remain unresolved. Option A may appear more decisive, but hiding or minimizing uncertainty could cause the recommendation to exceed what the evidence supports.</t>
+  </si>
+  <si>
+    <t>Question
+ A team designs this workflow: extract information, categorize it, draft a client summary, and perform a final quality review. Which change would most strengthen the chain?
+Option A
+ Add a review checkpoint before each output becomes input for the next stage, with clear criteria for approval.
+Option B
+ Use a different AI model at every stage so weaknesses from one model do not affect the complete workflow.
+Option C
+ Keep all four stages in one conversation so the AI can preserve the complete context without repeated instructions.
+Option D
+ Make the final quality review comprehensive enough to identify and correct errors introduced during any earlier stage.
+Correct Answer
+ A
+Explanation
+ Reviewing every handover prevents weak information from silently advancing through the chain. Option D provides an important final safeguard, but errors introduced early may already have shaped categorization and drafting, making them harder to trace and correct at the end.</t>
+  </si>
+  <si>
+    <t>Situation
+Nadine wants to find public library opening hours for an upcoming public holiday.
+Try It Yourself
+Identify the evidence behind an answer.
+1. Ask a harmless question about current information.
+2. Look for a source and publication date.
+3. Decide whether the answer shows live retrieval.
+Observe
+You can state what source was used or say that no source was shown.
+What Happened?
+The AI provides current opening hours from the library’s official website. Nadine opens the source and notices that different branches have different hours.
+Result
+She records the correct schedule for her chosen branch instead of relying on a general timetable.
+Key Insight
+You can now determine whether an AI answer uses live sources or stored model knowledge.</t>
+  </si>
+  <si>
+    <t>Situation
+Leila needs a short biography for a speaker at a neighbourhood science event.
+Try It Yourself
+Apply the three anti-hallucination habits.
+1. Provide a short factual paragraph.
+2. Request two facts using only that text.
+3. Match both answers to supporting sentences.
+Observe
+Every generated fact has visible support in the supplied material.
+What Happened?
+Leila compares the generated biography with the profile and removes one ambiguous description.
+Result
+Leila produces an accurate biography containing only confirmed experience, research interests, and the speaker’s current role.
+Key Insight
+You can now apply three habits that reduce unsupported AI claims.</t>
+  </si>
+  <si>
+    <t>Situation
+Aisha needs a slogan for a weekend repair café where volunteers help people fix household items.
+Try It Yourself
+Observe useful variation.
+1. Ask AI for three names for a fictional café.
+2. Repeat the exact request.
+3. Compare which names changed and which qualities remained.
+Observe
+You identify at least one difference and choose an option using a clear criterion.
+What Happened?
+Aisha receives several different slogans, but initially has no clear way to decide which one works best.
+With AI
+Aisha defines three criteria: friendly, under six words, and focused on repairing rather than replacing. She requests five options and evaluates each against those criteria.
+The alternatives still vary, but the rules remain stable.
+Result
+Aisha selects “Fix More, Waste Less” because it meets all three criteria. Variation gives her choices, while her criteria provide consistency.
+Key Insight
+You can now manage variation when AI produces different answers to the same request.</t>
+  </si>
+  <si>
+    <t>Situation
+Min wants a simple explanation of compound interest for a youth savings club.
+Try It Yourself
+Run a fair assistant comparison.
+1. Choose one harmless request.
+2. Use it unchanged in two available assistants.
+3. Compare the outputs using two criteria.
+Observe
+You choose one result and justify the choice with evidence from the outputs.
+What Happened?
+Min compares the responses for clarity, age suitability, example quality, and unnecessary jargon.
+One response is accurate but too technical. Another is simple but misses how interest builds over time. A third explains the idea clearly with a short numerical example.
+Result
+Min selects the third explanation for the club and records why it fits this audience. She does not assume the same assistant will be best for every future task.
+Key Insight
+You can now compare AI assistants using the same task and evaluation criteria.</t>
+  </si>
+  <si>
+    <t>Situation
+Hugo needs to explain a new recycling station to children visiting a nature centre.
+Try It Yourself
+Change content for a new audience.
+1. Choose one simple topic.
+2. Name two audiences with different knowledge levels.
+3. Write one sentence explaining what each audience needs.
+Observe
+The two audience descriptions would lead to visibly different content.
+What Happened?
+The resulting explanation uses familiar objects and short instructions. Hugo checks that each bin description matches the centre’s actual system.
+Result
+He creates a four-part sign that children can use to sort paper, containers, food waste, and general rubbish.
+Key Insight
+You can now adapt AI-generated content for a clearly defined audience.</t>
+  </si>
+  <si>
+    <t>Situation
+Tariq prepares a weekly update for his amateur basketball group.
+Try It Yourself
+Turn one repeated task into a system.
+1. Choose a harmless recurring task.
+2. Write its input, process, and review step.
+3. Identify which information changes each time.
+Observe
+Your system can be reused without redesigning the whole process.
+What Happened?
+Some updates focus only on results, others include upcoming games, and several forget venue information.
+With AI
+Tariq creates a three-part system:
+1. Provide this week’s approved notes.
+2. Generate sections for Results, Next Game, and Important Updates.
+3. Check every date and location against the notes.
+The weekly details change, but the process and output remain stable.
+Result
+Tariq produces a consistent update containing the same three useful sections every week, with dates and venues checked before publication.
+Key Insight
+You can now turn a recurring AI task into a simple, repeatable process.</t>
+  </si>
+  <si>
+    <t>Key Takeaways
+• Categories reveal different types of information.
+• Unconfirmed details must remain unconfirmed.
+• Clean structure makes the next action visible.
+Golden Rule
+Ask AI to organize what exists, not complete what is missing.
+Next Step
+Create three reusable headings for your next notes page before the conversation begins.</t>
+  </si>
+  <si>
+    <t>Key Takeaways
+• A win requires a useful result.
+• Different tasks may require different approaches.
+• Review turns AI output into human-approved work.
+Golden Rule
+Count completed outcomes, not AI conversations.
+Next Step
+Save your strongest use case as the first entry in a personal AI playbook.</t>
+  </si>
+  <si>
+    <t>Key Takeaways
+• Controlled tests reveal meaningful differences.
+• Polished language cannot replace source accuracy.
+• Tool choice should remain task-specific.
+Golden Rule
+Compare behaviours, not brands.
+Next Step
+Keep your rubric and repeat the test when your task or available models change.</t>
+  </si>
+  <si>
+    <t>Key Takeaways
+• Prompt improvement begins with diagnosis.
+• Useful detail solves a specific weakness.
+• Clear criteria reveal whether the revision worked.
+Golden Rule
+Do not decorate a broken prompt. Repair the missing instruction.
+Next Step
+Save the improved prompt with a short note explaining what changed and why.</t>
+  </si>
+  <si>
+    <t>Quiz</t>
+  </si>
+  <si>
+    <t>Step 1: Identify five safe tasks with different desired results.
+Step 2: Choose an appropriate AI approach for each task.
+Step 3: Review every output and record what changed because of your input.
+So in simple terms, use AI five times with purpose, variety, and human judgment.</t>
+  </si>
+  <si>
+    <t>Step 1: Define the final deliverable and the three intermediate outputs it requires.
+Step 2: Arrange the four stages in dependency order.
+Step 3: Review each output before passing it to the next stage.
+So in simple terms, build four necessary links and inspect every handover.</t>
+  </si>
+  <si>
+    <t>Situation
+Iris wants help planning a short presentation from notes stored in her workplace tools.
+What to Notice
+Iris first defines the task: create a five-slide outline from approved notes. She checks which assistant her organization allows for that content and whether it can work in the relevant environment.
+She then tests it with non-sensitive material before using workplace information.
+Why It Matters
+Iris selects an accessible, approved option and receives a five-slide outline without moving information into an unsuitable tool.
+Quick Check
+What should the learner trust, verify, choose, or keep under human control in this situation?
+Key Insight
+Choose among major AI assistants based on task and access.</t>
+  </si>
+  <si>
+    <t>Situation
+Diego considers buying an AI subscription after seeing several premium feature descriptions.
+What to Notice
+Diego writes down his actual needs: generate study questions, simplify difficult paragraphs, and create weekly revision plans. He tests each task with his available option and records whether a feature, limit, or quality issue blocks him.
+All three tasks work well enough for his current routine.
+Why It Matters
+Diego postpones the subscription and sets a clear trigger for reconsidering it: a repeated study task that his current access cannot complete reliably.
+Quick Check
+What should the learner trust, verify, choose, or keep under human control in this situation?
+Key Insight
+Decide whether a paid AI option supports a genuine need.</t>
+  </si>
+  <si>
+    <t>Situation
+Daniel lent a camera to a friend, who has twice missed the agreed return date. Daniel needs it for a course on Saturday.
+Without AI
+He keeps postponing the message because his first draft sounds angry: “You never respect deadlines.”
+With AI
+Daniel asks:
+“Draft a respectful but firm message. The camera was due back twice, and I need it by Friday evening for a Saturday course. Ask for a specific collection time. Do not accuse or threaten.”
+AI produces a calm draft. Daniel adds two collection windows he can genuinely offer.
+Result
+Daniel sends a factual message with a clear Friday deadline and receives confirmation that the camera will be collected at 18:30.</t>
+  </si>
+  <si>
+    <r>
+      <t>Situation
+Owen regularly needs to turn webinar descriptions into short entries for his learning journal.
+Try It Yourself
+Build a one-placeholder prompt.
+1. Choose a harmless recurring task.
+2. Write the fixed instruction.
+3. Replace the changing content with [INPUT].
+Observe
+Someone else could identify exactly what to replace and what result to expect.
+What Happened?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">
+Owen tests the prompt with a new webinar description. The structure is correct, but the result is too formal, so he adds: “Use clear first-person language.”
+Result
+Owen has a reusable prompt with one obvious placeholder and a consistent three-part output for future journal entries.
+Key Insight
+You can now create and save a reusable prompt for a recurring task.</t>
+    </r>
+  </si>
+  <si>
+    <t>Question
+ An AI assistant correctly explains several ways to reduce project delays, but the response does not help the team decide what to do next. Which follow-up is best?
+Option A
+ Provide a more detailed explanation of each method and include additional background on project-delay management.
+Option B
+ Using our six-week deadline and current staffing, recommend the first two actions, identify the appropriate owner role for each, and explain the priority.
+Option C
+ Rewrite the answer in simpler language so the team can understand the available methods more easily.
+Option D
+ Compare the advantages and disadvantages of every method before identifying which approaches are commonly preferred.
+Correct Answer
+ B
+Explanation
+ The original answer is correct but lacks practical application. Option B adds the team’s constraints and requests prioritized actions with ownership. Option D offers useful analysis, but it may still leave the team without a clear next step.</t>
+  </si>
+  <si>
+    <t>Some AI models prioritize speed for straightforward requests. Others are designed to spend more effort on tasks involving several constraints, connected decisions, or careful analysis.
+A longer response time does not automatically guarantee a better answer. Simple tasks rarely need heavy processing. The useful question is whether the task requires quick language support or deliberate problem-solving.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4474,6 +5967,13 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -4505,7 +6005,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4544,6 +6044,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -4851,7 +6357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K99"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -4863,9 +6369,10 @@
     <col min="9" max="9" width="64" customWidth="1"/>
     <col min="10" max="10" width="58" customWidth="1"/>
     <col min="11" max="11" width="64" customWidth="1"/>
+    <col min="13" max="13" width="81.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4879,7 +6386,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>650</v>
+        <v>633</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -4899,8 +6406,11 @@
       <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M1" s="16" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -4914,7 +6424,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
@@ -4932,8 +6442,11 @@
       <c r="K2" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M2" s="15" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -4947,7 +6460,7 @@
         <v>17</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>18</v>
@@ -4965,8 +6478,11 @@
       <c r="K3" s="5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M3" s="15" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -4980,7 +6496,7 @@
         <v>23</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>24</v>
@@ -4993,13 +6509,16 @@
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M4" s="15" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -5013,7 +6532,7 @@
         <v>28</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>29</v>
@@ -5026,13 +6545,16 @@
       </c>
       <c r="I5" s="13"/>
       <c r="J5" s="13" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M5" s="15" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -5046,7 +6568,7 @@
         <v>33</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>34</v>
@@ -5058,14 +6580,17 @@
         <v>36</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>604</v>
+        <v>747</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M6" s="15" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>1</v>
       </c>
@@ -5079,7 +6604,7 @@
         <v>38</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>39</v>
@@ -5097,8 +6622,11 @@
       <c r="K7" s="5" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M7" s="15" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>1</v>
       </c>
@@ -5112,7 +6640,7 @@
         <v>44</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>45</v>
@@ -5130,8 +6658,11 @@
       <c r="K8" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M8" s="15" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>1</v>
       </c>
@@ -5145,7 +6676,7 @@
         <v>50</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>51</v>
@@ -5158,13 +6689,16 @@
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M9" s="15" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>1</v>
       </c>
@@ -5178,12 +6712,12 @@
         <v>55</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="14" t="s">
         <v>57</v>
       </c>
       <c r="H10" s="3" t="s">
@@ -5191,13 +6725,16 @@
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M10" s="15" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>1</v>
       </c>
@@ -5211,26 +6748,29 @@
         <v>60</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="13" t="s">
         <v>63</v>
       </c>
       <c r="I11" s="5"/>
-      <c r="J11" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J11" s="13" t="s">
+        <v>598</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>740</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>1</v>
       </c>
@@ -5241,29 +6781,32 @@
         <v>11</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>1</v>
       </c>
@@ -5274,29 +6817,32 @@
         <v>12</v>
       </c>
       <c r="D13" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>651</v>
-      </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>75</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>1</v>
       </c>
@@ -5307,29 +6853,32 @@
         <v>13</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>1</v>
       </c>
@@ -5340,29 +6889,32 @@
         <v>14</v>
       </c>
       <c r="D15" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>651</v>
-      </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="H15" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="I15" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>1</v>
       </c>
@@ -5373,29 +6925,32 @@
         <v>15</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+      <c r="M16" s="15" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>1</v>
       </c>
@@ -5406,29 +6961,32 @@
         <v>16</v>
       </c>
       <c r="D17" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>651</v>
-      </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="H17" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>1</v>
       </c>
@@ -5439,29 +6997,32 @@
         <v>17</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="I18" s="3" t="s">
-        <v>610</v>
+        <v>748</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
         <v>1</v>
       </c>
@@ -5472,29 +7033,32 @@
         <v>18</v>
       </c>
       <c r="D19" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>651</v>
-      </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="I19" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>108</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+      <c r="M19" s="15" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>1</v>
       </c>
@@ -5505,29 +7069,32 @@
         <v>19</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3"/>
+      <c r="J20" s="14" t="s">
+        <v>750</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M20" s="15" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
         <v>1</v>
       </c>
@@ -5538,2667 +7105,2905 @@
         <v>20</v>
       </c>
       <c r="D21" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>651</v>
-      </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="H21" s="13" t="s">
+        <v>745</v>
+      </c>
+      <c r="I21" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="J21" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="I21" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K21" s="13" t="s">
+        <v>741</v>
+      </c>
+      <c r="M21" s="15" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>2</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C22" s="2">
         <v>21</v>
       </c>
       <c r="D22" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="I22" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="J22" s="3"/>
+      <c r="K22" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M22" s="15" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
         <v>2</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C23" s="4">
         <v>22</v>
       </c>
       <c r="D23" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+      <c r="M23" s="15" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>2</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C24" s="2">
         <v>23</v>
       </c>
       <c r="D24" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
         <v>2</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C25" s="4">
         <v>24</v>
       </c>
       <c r="D25" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>142</v>
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>140</v>
+      </c>
+      <c r="M25" s="15" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>2</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C26" s="2">
         <v>25</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="I26" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>146</v>
+      </c>
+      <c r="M26" s="15" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
         <v>2</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C27" s="4">
         <v>26</v>
       </c>
       <c r="D27" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>153</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+      <c r="M27" s="15" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>2</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C28" s="2">
         <v>27</v>
       </c>
       <c r="D28" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="I28" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>157</v>
+      </c>
+      <c r="M28" s="15" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
         <v>2</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C29" s="4">
         <v>28</v>
       </c>
       <c r="D29" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H29" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="F29" s="5" t="s">
+      <c r="I29" s="5"/>
+      <c r="J29" s="13" t="s">
+        <v>734</v>
+      </c>
+      <c r="K29" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M29" s="15" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>2</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C30" s="2">
         <v>29</v>
       </c>
       <c r="D30" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="5" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>167</v>
+      </c>
+      <c r="M30" s="15" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
         <v>2</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C31" s="4">
         <v>30</v>
       </c>
       <c r="D31" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="F31" s="5" t="s">
+      <c r="I31" s="5"/>
+      <c r="J31" s="13" t="s">
+        <v>735</v>
+      </c>
+      <c r="K31" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5" t="s">
-        <v>618</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M31" s="15" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>2</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C32" s="2">
         <v>31</v>
       </c>
       <c r="D32" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="I32" s="3"/>
+      <c r="J32" s="14" t="s">
+        <v>736</v>
+      </c>
+      <c r="K32" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M32" s="15" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
         <v>2</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C33" s="4">
         <v>32</v>
       </c>
       <c r="D33" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="I33" s="5" t="s">
         <v>181</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>185</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>182</v>
+      </c>
+      <c r="M33" s="15" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>2</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C34" s="2">
         <v>33</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="14" t="s">
-        <v>620</v>
+        <v>737</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>187</v>
+      </c>
+      <c r="M34" s="15" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4">
         <v>2</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C35" s="4">
         <v>34</v>
       </c>
       <c r="D35" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I35" s="5" t="s">
         <v>192</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>196</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+      <c r="M35" s="15" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>2</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C36" s="2">
         <v>35</v>
       </c>
       <c r="D36" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="J36" s="3"/>
       <c r="K36" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>199</v>
+      </c>
+      <c r="M36" s="15" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4">
         <v>2</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C37" s="4">
         <v>36</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="13" t="s">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+      <c r="M37" s="15" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>2</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C38" s="2">
         <v>37</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="14" t="s">
-        <v>622</v>
+        <v>607</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>209</v>
+      </c>
+      <c r="M38" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4">
         <v>2</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C39" s="4">
         <v>38</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="I39" s="5"/>
       <c r="J39" s="13" t="s">
-        <v>623</v>
+        <v>608</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>214</v>
+      </c>
+      <c r="M39" s="15" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>2</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C40" s="2">
         <v>39</v>
       </c>
       <c r="D40" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>223</v>
       </c>
       <c r="J40" s="3"/>
       <c r="K40" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+      <c r="M40" s="15" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4">
         <v>2</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C41" s="4">
         <v>40</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I41" s="5"/>
       <c r="J41" s="13" t="s">
-        <v>624</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>609</v>
+      </c>
+      <c r="K41" s="13" t="s">
+        <v>742</v>
+      </c>
+      <c r="M41" s="15" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>3</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C42" s="2">
         <v>41</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>230</v>
+      </c>
+      <c r="M42" s="15" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4">
         <v>3</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C43" s="4">
         <v>42</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="I43" s="5"/>
       <c r="J43" s="13" t="s">
-        <v>626</v>
+        <v>611</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>235</v>
+      </c>
+      <c r="M43" s="15" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>3</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C44" s="2">
         <v>43</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="s">
-        <v>627</v>
+        <v>612</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>240</v>
+      </c>
+      <c r="M44" s="15" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4">
         <v>3</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C45" s="4">
         <v>44</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="I45" s="5"/>
       <c r="J45" s="13" t="s">
-        <v>628</v>
+        <v>613</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+      <c r="M45" s="15" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>3</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C46" s="2">
         <v>45</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="I46" s="3"/>
       <c r="J46" s="14" t="s">
-        <v>629</v>
+        <v>614</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>250</v>
+      </c>
+      <c r="M46" s="15" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4">
         <v>3</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C47" s="4">
         <v>46</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="I47" s="5"/>
       <c r="J47" s="13" t="s">
-        <v>630</v>
+        <v>738</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>255</v>
+      </c>
+      <c r="M47" s="15" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>3</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C48" s="2">
         <v>47</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="s">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>260</v>
+      </c>
+      <c r="M48" s="15" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4">
         <v>3</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C49" s="4">
         <v>48</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="I49" s="5"/>
       <c r="J49" s="13" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>265</v>
+      </c>
+      <c r="M49" s="15" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>3</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C50" s="2">
         <v>49</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="14" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>270</v>
+      </c>
+      <c r="M50" s="15" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4">
         <v>3</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C51" s="4">
         <v>50</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="I51" s="5"/>
       <c r="J51" s="13" t="s">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>275</v>
+      </c>
+      <c r="M51" s="15" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>3</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C52" s="2">
         <v>51</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I52" s="3"/>
       <c r="J52" s="14" t="s">
-        <v>635</v>
+        <v>619</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+      <c r="M52" s="15" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4">
         <v>3</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C53" s="4">
         <v>52</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="I53" s="5"/>
       <c r="J53" s="13" t="s">
-        <v>636</v>
+        <v>620</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>285</v>
+      </c>
+      <c r="M53" s="15" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>3</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C54" s="2">
         <v>53</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="I54" s="3"/>
       <c r="J54" s="14" t="s">
-        <v>637</v>
+        <v>621</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>290</v>
+      </c>
+      <c r="M54" s="15" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4">
         <v>3</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C55" s="4">
         <v>54</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="I55" s="5"/>
       <c r="J55" s="13" t="s">
-        <v>638</v>
+        <v>622</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>295</v>
+      </c>
+      <c r="M55" s="15" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>3</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C56" s="2">
         <v>55</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="I56" s="3"/>
       <c r="J56" s="14" t="s">
-        <v>639</v>
+        <v>623</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>300</v>
+      </c>
+      <c r="M56" s="15" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4">
         <v>3</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C57" s="4">
         <v>56</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="I57" s="5"/>
       <c r="J57" s="13" t="s">
-        <v>640</v>
+        <v>624</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>305</v>
+      </c>
+      <c r="M57" s="15" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>3</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C58" s="2">
         <v>57</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="I58" s="3"/>
       <c r="J58" s="14" t="s">
-        <v>641</v>
+        <v>625</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>310</v>
+      </c>
+      <c r="M58" s="15" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4">
         <v>3</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C59" s="4">
         <v>58</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="I59" s="5"/>
       <c r="J59" s="13" t="s">
-        <v>642</v>
+        <v>626</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>315</v>
+      </c>
+      <c r="M59" s="15" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>3</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C60" s="2">
         <v>59</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="I60" s="14"/>
       <c r="J60" s="14" t="s">
-        <v>643</v>
+        <v>627</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>320</v>
+      </c>
+      <c r="M60" s="15" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4">
         <v>3</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C61" s="4">
         <v>60</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="I61" s="5"/>
       <c r="J61" s="13" t="s">
-        <v>644</v>
+        <v>628</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>325</v>
+      </c>
+      <c r="M61" s="15" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>3</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C62" s="2">
         <v>61</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="I62" s="14" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="J62" s="14"/>
       <c r="K62" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+      <c r="M62" s="15" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4">
         <v>3</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C63" s="4">
         <v>62</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="J63" s="5"/>
       <c r="K63" s="5" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>337</v>
+      </c>
+      <c r="M63" s="15" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>3</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C64" s="2">
         <v>63</v>
       </c>
       <c r="D64" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="J64" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="E64" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="F64" s="3" t="s">
+      <c r="K64" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="G64" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M64" s="15" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4">
         <v>3</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C65" s="4">
         <v>64</v>
       </c>
       <c r="D65" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="K65" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="E65" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="I65" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="J65" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="K65" s="5" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M65" s="15" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>3</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C66" s="2">
         <v>65</v>
       </c>
       <c r="D66" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="K66" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M66" s="15" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4">
         <v>3</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C67" s="4">
         <v>66</v>
       </c>
       <c r="D67" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K67" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="H67" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="I67" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="J67" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="K67" s="5" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M67" s="15" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>3</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C68" s="2">
         <v>67</v>
       </c>
       <c r="D68" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="I68" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="J68" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="K68" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="E68" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="I68" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="J68" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M68" s="15" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4">
         <v>3</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C69" s="4">
         <v>68</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="K69" s="5" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>377</v>
+      </c>
+      <c r="K69" s="13" t="s">
+        <v>743</v>
+      </c>
+      <c r="M69" s="15" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>4</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C70" s="2">
         <v>69</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="I70" s="14"/>
       <c r="J70" s="14" t="s">
-        <v>645</v>
+        <v>739</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>383</v>
+      </c>
+      <c r="M70" s="15" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4">
         <v>4</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C71" s="4">
         <v>70</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="I71" s="5"/>
       <c r="J71" s="13" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>388</v>
+      </c>
+      <c r="M71" s="15" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>4</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C72" s="2">
         <v>71</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="I72" s="3"/>
       <c r="J72" s="14" t="s">
-        <v>647</v>
+        <v>630</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>393</v>
+      </c>
+      <c r="M72" s="15" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4">
         <v>4</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C73" s="4">
         <v>72</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="I73" s="5"/>
       <c r="J73" s="13" t="s">
-        <v>648</v>
+        <v>631</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>398</v>
+      </c>
+      <c r="M73" s="15" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>4</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C74" s="2">
         <v>73</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="I74" s="3"/>
       <c r="J74" s="14" t="s">
-        <v>649</v>
+        <v>632</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>403</v>
+      </c>
+      <c r="M74" s="15" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4">
         <v>4</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C75" s="4">
         <v>74</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="J75" s="13"/>
       <c r="K75" s="5" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>409</v>
+      </c>
+      <c r="M75" s="15" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>4</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C76" s="2">
         <v>75</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>416</v>
+      </c>
+      <c r="M76" s="15" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4">
         <v>4</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C77" s="4">
         <v>76</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>423</v>
+      </c>
+      <c r="M77" s="15" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>4</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C78" s="2">
         <v>77</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="I78" s="14" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>430</v>
+      </c>
+      <c r="M78" s="15" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4">
         <v>4</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C79" s="4">
         <v>78</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>437</v>
+      </c>
+      <c r="M79" s="15" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>4</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C80" s="2">
         <v>79</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>444</v>
+      </c>
+      <c r="M80" s="15" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="4">
         <v>4</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C81" s="4">
         <v>80</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="I81" s="13" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>451</v>
+      </c>
+      <c r="M81" s="15" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>4</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C82" s="2">
         <v>81</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>458</v>
+      </c>
+      <c r="M82" s="15" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="4">
         <v>4</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C83" s="4">
         <v>82</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="K83" s="5" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>465</v>
+      </c>
+      <c r="M83" s="15" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>4</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C84" s="2">
         <v>83</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>472</v>
+      </c>
+      <c r="M84" s="15" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="4">
         <v>4</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C85" s="4">
         <v>84</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>479</v>
+      </c>
+      <c r="M85" s="15" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>4</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C86" s="2">
         <v>85</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>486</v>
+      </c>
+      <c r="M86" s="15" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4">
         <v>4</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C87" s="4">
         <v>86</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>493</v>
+      </c>
+      <c r="M87" s="15" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>4</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C88" s="2">
         <v>87</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>500</v>
+      </c>
+      <c r="M88" s="15" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="4">
         <v>4</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C89" s="4">
         <v>88</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="I89" s="5" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>507</v>
+      </c>
+      <c r="M89" s="15" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>4</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C90" s="2">
         <v>89</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>514</v>
+      </c>
+      <c r="M90" s="15" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="4">
         <v>4</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C91" s="4">
         <v>90</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="J91" s="5" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="K91" s="5" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>521</v>
+      </c>
+      <c r="M91" s="15" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>4</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C92" s="2">
         <v>91</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>528</v>
+      </c>
+      <c r="M92" s="15" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="4">
         <v>4</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C93" s="4">
         <v>92</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="I93" s="5" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="J93" s="5" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="K93" s="5" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>535</v>
+      </c>
+      <c r="M93" s="15" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>4</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C94" s="2">
         <v>93</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>542</v>
+      </c>
+      <c r="M94" s="15" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="4">
         <v>4</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C95" s="4">
         <v>94</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="I95" s="5" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>549</v>
+      </c>
+      <c r="M95" s="15" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>4</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C96" s="2">
         <v>95</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>556</v>
+      </c>
+      <c r="M96" s="15" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="4">
         <v>4</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C97" s="4">
         <v>96</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="J97" s="5" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="K97" s="5" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>563</v>
+      </c>
+      <c r="M97" s="15" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>4</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C98" s="2">
         <v>97</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+        <v>570</v>
+      </c>
+      <c r="M98" s="15" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="4">
         <v>4</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C99" s="4">
         <v>98</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="H99" s="5" t="s">
-        <v>581</v>
+        <v>573</v>
+      </c>
+      <c r="H99" s="13" t="s">
+        <v>746</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="K99" s="5" t="s">
-        <v>584</v>
+        <v>576</v>
+      </c>
+      <c r="M99" s="15" t="s">
+        <v>733</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K99" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8215,12 +10020,12 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="B3" s="8">
         <v>98</v>
@@ -8228,7 +10033,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="B4" s="8">
         <v>1</v>
@@ -8236,7 +10041,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="B5" s="8">
         <v>98</v>
@@ -8244,31 +10049,31 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="B9" s="8">
         <v>0</v>
@@ -8276,7 +10081,7 @@
     </row>
     <row r="10" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="B10" s="8">
         <v>0</v>
@@ -8284,7 +10089,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="B11" s="8">
         <v>0</v>
@@ -8292,15 +10097,15 @@
     </row>
     <row r="12" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.4">
       <c r="A15" s="9" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -8311,23 +10116,23 @@
         <v>3</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="15" t="s">
-        <v>590</v>
-      </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
+      <c r="A17" s="17" t="s">
+        <v>582</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.35">
       <c r="A19" s="10" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -8338,19 +10143,19 @@
         <v>3</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="15" t="s">
-        <v>590</v>
-      </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
+      <c r="A21" s="17" t="s">
+        <v>582</v>
+      </c>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
     </row>
   </sheetData>
   <autoFilter ref="A16:D16" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
